--- a/IT조직_비교표_공공기관274.xlsx
+++ b/IT조직_비교표_공공기관274.xlsx
@@ -13121,17 +13121,17 @@
       </c>
       <c r="F169" s="3" t="inlineStr">
         <is>
-          <t>정보운영관리실 (행정정보화 전담) / 기획처 기획조정실(정보화사업 총괄)</t>
+          <t>한국학도서관 (정보운영관리실·한국학정보화실 포함, 정보화 총괄) / 정보화사업 주관은 기획처 기획조정실</t>
         </is>
       </c>
       <c r="G169" s="3" t="inlineStr">
         <is>
-          <t>실 (사무국·행정조직 내) — 확인불가 요소 있음</t>
+          <t>처·실(본부 산하) — 정보운영관리실·한국학정보화실이 한국학도서관(처급 단위) 산하 실</t>
         </is>
       </c>
       <c r="H169" s="3" t="inlineStr">
         <is>
-          <t>정보운영관리실 (행정시스템·ERP·정보인프라 운영), 한국학지식정보센터(구 한국학정보센터)·인문정보학연구실 (연구·자료 디지털화)</t>
+          <t>정보운영관리실(행정시스템·ERP·정보인프라 운영), 한국학정보화실(한국학자료 정보화), 문헌정보팀 — 모두 한국학도서관 산하</t>
         </is>
       </c>
       <c r="I169" s="3" t="inlineStr">
@@ -13151,7 +13151,7 @@
       </c>
       <c r="L169" s="3" t="inlineStr">
         <is>
-          <t>기획처장 또는 사무국장 총괄 (추정)</t>
+          <t>정보화사업 주관 기획처 기획조정실 / 시스템운영은 한국학도서관 정보운영관리실 (전담 CIO 직위 미확인)</t>
         </is>
       </c>
       <c r="M169" s="3" t="inlineStr">
@@ -13161,7 +13161,7 @@
       </c>
       <c r="N169" s="3" t="inlineStr">
         <is>
-          <t>중(공식 1출처 + 공식 보조자료)</t>
+          <t>상(공식 조직도 원문에서 한국학도서관 산하 정보운영관리실·한국학정보화실 트리 확인 + 보조자료)</t>
         </is>
       </c>
       <c r="O169" s="3" t="inlineStr">
@@ -13196,17 +13196,17 @@
       </c>
       <c r="F170" s="3" t="inlineStr">
         <is>
-          <t>확인불가 (별도 정보화 본부·처 없음 / '전산실'이 행정 단위로 존재 — 기획조정실·행정실과 동일 층(5F)에 배치, 기획조정실 또는 행정실 산하 운영 추정)</t>
+          <t>정보전산팀 (관리부 계열 / 전산·정보시스템·기술보안 담당)</t>
         </is>
       </c>
       <c r="G170" s="3" t="inlineStr">
         <is>
-          <t>팀·실 이하 (전산실 단위 — 독립 본부·처 아님)</t>
+          <t>팀 (관리부·홍보실과 병렬되는 팀 단위 — 독립 본부·처 아님)</t>
         </is>
       </c>
       <c r="H170" s="3" t="inlineStr">
         <is>
-          <t>전산실(전산·정보시스템 담당) — 그 외 세부 하위팀은 확인불가</t>
+          <t>정보전산팀(전산·정보시스템 운영, 기술보안 담당) — 그 외 세부 하위팀은 확인불가</t>
         </is>
       </c>
       <c r="I170" s="3" t="inlineStr">
@@ -13226,17 +13226,17 @@
       </c>
       <c r="L170" s="3" t="inlineStr">
         <is>
-          <t>확인불가 (기획조정실장 겸임 추정)</t>
+          <t>확인불가 (전담 CIO 직위 미확인 / 정보전산팀이 정보시스템 총괄)</t>
         </is>
       </c>
       <c r="M170" s="3" t="inlineStr">
         <is>
-          <t>확인불가</t>
+          <t>진료처장(개인정보보호책임자 겸 정보보호 총괄) — 기술보안 실무는 정보전산팀 담당</t>
         </is>
       </c>
       <c r="N170" s="3" t="inlineStr">
         <is>
-          <t>중 (층별안내 등으로 '전산실' 존재 확인, 다만 조직도 트리·소속 라인은 이미지로만 제공되어 정확한 소속 미확정)</t>
+          <t>상 (공식 개인정보처리방침 원문에서 정보전산팀 명칭·기술보안 담당자·개인정보보호책임자(진료처장) 직접 확인)</t>
         </is>
       </c>
       <c r="O170" s="3" t="inlineStr">
@@ -13281,7 +13281,7 @@
       </c>
       <c r="H171" s="3" t="inlineStr">
         <is>
-          <t>정보화 담당 (정보화사업·전산인프라·정보보안·공공데이터 — 기획경영본부 행정 부서 산하, 정확한 팀명 확인불가)</t>
+          <t>재무·정보팀 (기획경영본부 산하 / 정보화사업·전산인프라·정보보안·공공데이터 담당)</t>
         </is>
       </c>
       <c r="I171" s="3" t="inlineStr">
@@ -13301,17 +13301,17 @@
       </c>
       <c r="L171" s="3" t="inlineStr">
         <is>
-          <t>확인불가 (기획경영본부장 겸임 추정)</t>
+          <t>기획경영본부장 총괄 (재무·정보팀 소관) — 전담 CIO 직위는 미확인</t>
         </is>
       </c>
       <c r="M171" s="3" t="inlineStr">
         <is>
-          <t>확인불가 (정보보안 담당자 별도 지정 — 기획경영본부 정보화 담당)</t>
+          <t>재무·정보팀 정보보안 담당자 (기획경영본부 산하) — 별도 CISO 임원 직위 미확인</t>
         </is>
       </c>
       <c r="N171" s="3" t="inlineStr">
         <is>
-          <t>중 (공식 홈페이지 직원검색에서 정보화 담당자·연구본부 구성 확인, 다만 조직도 본문이 JS 렌더링되어 행정 IT 팀명 직접 확인 제한)</t>
+          <t>상 (공식 홈페이지 직원검색 원문에서 정보화 담당자 소속 '재무·정보팀'(기획경영본부 산하)·담당분야 직접 확인)</t>
         </is>
       </c>
       <c r="O171" s="3" t="inlineStr">
@@ -13356,42 +13356,42 @@
       </c>
       <c r="H172" s="3" t="inlineStr">
         <is>
-          <t>임업통계실 등 산림정보·정보화 관련 부서 (정확한 하위 실/팀명 일부 확인불가)</t>
+          <t>산림공간정보실, 임업통계실, 산림빅데이터산업실 (산림정보본부 산하)</t>
         </is>
       </c>
       <c r="I172" s="3" t="inlineStr">
         <is>
-          <t>없음 (조직 차원 AI 전담부서 미확인)</t>
+          <t>있음 (사업 단위 — 산림빅데이터·AI 전담 실)</t>
         </is>
       </c>
       <c r="J172" s="3" t="inlineStr">
         <is>
-          <t>해당없음</t>
+          <t>산림빅데이터산업실 (산림빅데이터 플랫폼·공공 AI·데이터 협력 사업 수행)</t>
         </is>
       </c>
       <c r="K172" s="3" t="inlineStr">
         <is>
-          <t>해당없음</t>
+          <t>실 (산림정보본부 산하)</t>
         </is>
       </c>
       <c r="L172" s="3" t="inlineStr">
         <is>
-          <t>확인불가 (산림정보본부장 겸임 추정)</t>
+          <t>산림정보본부장 총괄 (추정) — 전담 CIO 직위 미확인</t>
         </is>
       </c>
       <c r="M172" s="3" t="inlineStr">
         <is>
-          <t>확인불가</t>
+          <t>산림정보본부 정보화 담당 소관 (추정) — 별도 CISO 직위 미확인</t>
         </is>
       </c>
       <c r="N172" s="3" t="inlineStr">
         <is>
-          <t>중 (공식 홈페이지 조직 소개·직원안내 및 기관 소개책자 PDF로 본부 구성 확인, AI는 보도자료 다수 확인)</t>
+          <t>상 (산림정보본부 산하 산림공간정보실·임업통계실·산림빅데이터산업실을 정부사업공고·data.go.kr API 제공부서 메타데이터 등 복수 출처로 교차 확인)</t>
         </is>
       </c>
       <c r="O172" s="3" t="inlineStr">
         <is>
-          <t>4본부 1단 11팀 체계(기획운영본부·산업지원본부·인증평가본부·산림정보본부 + 임업지식·신기술지원단). '임업정보 다드림(林)' 산림정보 플랫폼 운영. AI는 산림과학기술 R&amp;D·아이디어 공모전(NIA 협력 'AI혁신 및 데이터스페이스 구축') 등 사업 차원에서 적극 추진 중이나 전담 조직은 미신설.</t>
+          <t>4본부 체계(기획운영본부·산업지원본부·인증평가본부·산림정보본부). 산림정보본부 산하에 산림공간정보실·임업통계실·산림빅데이터산업실. '임업정보 다드림(林)' 산림정보 플랫폼 및 '산림빅데이터 플랫폼·거래소'(bigdata-forest.kr) 운영. 산림빅데이터산업실이 공공 빅데이터·AI 협력(8개 기관 MOU), 산림분야 빅데이터·AI 활용 창업경진대회, 2025 인공지능&amp;빅데이터쇼 참가 등 AI·데이터 사업을 전담. 다만 '인공지능실/AI팀' 명칭의 순수 AI 전담조직은 아니며 빅데이터·데이터산업 중심 실.</t>
         </is>
       </c>
     </row>
@@ -13506,7 +13506,7 @@
       </c>
       <c r="H174" s="3" t="inlineStr">
         <is>
-          <t>정보화 담당 팀 (경영지원팀이 공공데이터 제공 담당 등 수행 / 정확한 정보화·정보보안 팀명 확인불가)</t>
+          <t>경영지원팀 (경영기획본부 산하 / 정보시스템·IDC·CLOUD 통합 유지관리·공공데이터·개인정보보호 담당)</t>
         </is>
       </c>
       <c r="I174" s="3" t="inlineStr">
@@ -13526,22 +13526,22 @@
       </c>
       <c r="L174" s="3" t="inlineStr">
         <is>
-          <t>확인불가 (경영기획본부장 겸임 추정)</t>
+          <t>경영기획본부장 총괄 (개인정보보호책임자(CPO)를 경영기획본부장이 겸임)</t>
         </is>
       </c>
       <c r="M174" s="3" t="inlineStr">
         <is>
-          <t>확인불가 (정보보호·전산시스템 담당자 별도 지정)</t>
+          <t>경영지원팀 소관 (정보시스템·정보보호 담당) — 별도 CISO 임원 직위 미확인</t>
         </is>
       </c>
       <c r="N174" s="3" t="inlineStr">
         <is>
-          <t>중 (공식 홈페이지에서 조직 규모·본부 구성 확인, 정보화 팀명은 조직도 본문 JS 렌더링으로 직접 미확인 / 공공데이터 담당부서 확인)</t>
+          <t>상 (2025.09.12 개정 개인정보처리방침 원문에서 CPO=경영기획본부장, 개인정보·정보시스템 담당부서=경영지원팀 직접 확인 + 공식 조직도 본부·팀 구성 확인)</t>
         </is>
       </c>
       <c r="O174" s="3" t="inlineStr">
         <is>
-          <t>2026.4.1 시행 조직: 1처 3본부 1극장 1관 1실 1센터 1원 13팀. 위원장-사무처장 체계, 경영기획본부가 경영·정보화 총괄. 아르코예술기록원이 예술기록 디지털아카이브 운영(정보화 사업 측면). 국가문화예술지원시스템(NCAS) 등 다수 정보시스템 운영.</t>
+          <t>2026.4.1 시행 조직: 1처 3본부 1극장 1관 1실 1센터 1원 13팀. 위원장-사무처장 체계. 경영기획본부 산하 3팀(기획조정팀·경영지원팀·인사소통팀) 중 경영지원팀이 정보화·전산을 담당(IDC/CLOUD 시스템 통합 유지관리 위탁감독). 국가문화예술지원시스템(NCAS), 아트누리, 공공미술포털 등 다수 정보시스템 운영. 아르코예술기록원이 예술기록 디지털아카이브 운영.</t>
         </is>
       </c>
     </row>
@@ -13661,37 +13661,37 @@
       </c>
       <c r="I176" s="3" t="inlineStr">
         <is>
-          <t>확인불가</t>
+          <t>없음 (조직 차원 AI 전담부서 미확인 — 기술혁신본부가 스마트HACCP·AI 기반 분석모델 사업을 사업 단위로 수행)</t>
         </is>
       </c>
       <c r="J176" s="3" t="inlineStr">
         <is>
-          <t>확인불가 (별도 AI 전담부서는 미확인. 스마트HACCP·기술혁신본부가 AI 기반 분석모델 사업 일부 수행)</t>
+          <t>해당없음</t>
         </is>
       </c>
       <c r="K176" s="3" t="inlineStr">
         <is>
-          <t>확인불가</t>
+          <t>해당없음</t>
         </is>
       </c>
       <c r="L176" s="3" t="inlineStr">
         <is>
-          <t>확인불가 (IT전략팀이 속한 기술혁신본부장이 정보화 총괄로 추정)</t>
+          <t>기술혁신본부장 총괄 (정보화·스마트HACCP 사업 주관, 인증사업이사 산하) — 전담 CIO 직위 미확인</t>
         </is>
       </c>
       <c r="M176" s="3" t="inlineStr">
         <is>
-          <t>확인불가</t>
+          <t>기술혁신본부(IT전략팀) 소관 (추정) — 별도 CISO 임원 직위 미확인</t>
         </is>
       </c>
       <c r="N176" s="3" t="inlineStr">
         <is>
-          <t>중(공식성 보조 출처 1 + 보도 보조)</t>
+          <t>중(위키 조직표 + 공식 누리집·data.go.kr 제공부서(기술혁신본부) 교차 / 팀명 1차자료는 위키 의존)</t>
         </is>
       </c>
       <c r="O176" s="3" t="inlineStr">
         <is>
-          <t>인증사업이사 산하에 기술혁신본부(스마트기획팀·스마트운영팀·IT전략팀)를 두어 스마트HACCP 등 정보화·디지털 사업 담당. 음료 제조업 대상 AI 기반 분석모델 개발 민관 협력 추진 보도 있음(AI 전담조직과는 별개).</t>
+          <t>인증사업이사 산하에 기술혁신본부(스마트기획팀·스마트운영팀·IT전략팀)를 두어 스마트HACCP 등 정보화·디지털 사업 담당. 스마트HACCP 데이터·서비스(축산물 스마트HACCP 인증정보 등) 제공부서가 기술혁신본부로 확인됨(data.go.kr 메타데이터). 음료 제조업 대상 AI 기반 분석모델 개발 민관 협력 추진 보도 있음 — 사업 단위이며 AI 전담조직과는 별개.</t>
         </is>
       </c>
     </row>
@@ -13731,7 +13731,7 @@
       </c>
       <c r="H177" s="3" t="inlineStr">
         <is>
-          <t>정보화전략부, 청소년안전망데이터센터(데이터 운영)</t>
+          <t>정보화전략부, 개인정보보호팀, 청소년안전망데이터센터(데이터 운영)</t>
         </is>
       </c>
       <c r="I177" s="3" t="inlineStr">
@@ -13751,22 +13751,22 @@
       </c>
       <c r="L177" s="3" t="inlineStr">
         <is>
-          <t>확인불가</t>
+          <t>확인불가 (정보화전략부 소관, 별도 CIO 직위 미확인)</t>
         </is>
       </c>
       <c r="M177" s="3" t="inlineStr">
         <is>
-          <t>확인불가</t>
+          <t>확인불가 (별도 CISO 직위 미표기). 개인정보보호책임자(CPO)=통합지원본부장(노성덕), 개인정보보호팀(팀장 남용수) 별도 운영. 개인정보 안전성 확보조치(관리·기술·물리) 시행</t>
         </is>
       </c>
       <c r="N177" s="3" t="inlineStr">
         <is>
-          <t>중(공식 조직 명칭 1출처 + 보조 출처)</t>
+          <t>상(공식 조직 명칭 + 개인정보처리방침(공식) 교차 확인)</t>
         </is>
       </c>
       <c r="O177" s="3" t="inlineStr">
         <is>
-          <t>조직이 다수의 '부' 단위(기획조정부·경영관리부 등)로 편제된 연구·사업 기관. 정보화전략부가 정보화 총괄. 청소년안전망데이터센터에서 청소년안전망 데이터 수집·관리. AI는 정책연구 주제로 다룸(생성형 AI 리터러시 연구 등).</t>
+          <t>조직이 다수의 '부' 단위(기획조정부·경영관리부 등)로 편제된 연구·사업 기관. 정보화전략부가 정보화 총괄, 중장기 정보화전략계획(ISP) 수립. 개인정보보호는 통합지원본부장(CPO)·개인정보보호팀이 담당. 청소년안전망데이터센터에서 청소년안전망 데이터 수집·관리. AI는 정책연구 주제로 다룸(생성형 AI 리터러시 연구 등). 2022년 개인정보 관리수준 진단 'B'등급.</t>
         </is>
       </c>
     </row>
@@ -13796,17 +13796,17 @@
       </c>
       <c r="F178" s="3" t="inlineStr">
         <is>
-          <t>정보화전략부</t>
+          <t>정보화전략부 (경영전략본부 산하)</t>
         </is>
       </c>
       <c r="G178" s="3" t="inlineStr">
         <is>
-          <t>부(본부 산하 추정)</t>
+          <t>부(본부 산하)</t>
         </is>
       </c>
       <c r="H178" s="3" t="inlineStr">
         <is>
-          <t>정보화전략부, 정보보안팀</t>
+          <t>정보화전략부 (정보시스템 운영·정보보안·개인정보·교육관리통합시스템 담당)</t>
         </is>
       </c>
       <c r="I178" s="3" t="inlineStr">
@@ -13816,7 +13816,7 @@
       </c>
       <c r="J178" s="3" t="inlineStr">
         <is>
-          <t>확인불가 (별도 AI 전담부서 미확인)</t>
+          <t>확인불가 (별도 AI 전담부서 미확인. 의료 AI 공통역량과정 등 교육콘텐츠로 AI 다룸)</t>
         </is>
       </c>
       <c r="K178" s="3" t="inlineStr">
@@ -13826,22 +13826,22 @@
       </c>
       <c r="L178" s="3" t="inlineStr">
         <is>
-          <t>확인불가 (정보화전략부 소관 본부장 겸임 추정)</t>
+          <t>경영전략본부장 겸임(추정) — 정보화전략부가 경영전략본부 소관, 개인정보보호책임자(CPO)도 경영전략본부장(김준태)</t>
         </is>
       </c>
       <c r="M178" s="3" t="inlineStr">
         <is>
-          <t>확인불가 (정보보안팀 운영)</t>
+          <t>확인불가 (별도 CISO 직위 미표기). 개인정보보호책임자(CPO)=경영전략본부장(김준태), 담당부서=정보화전략부. 정보화전략부가 정보보안·접근통제·암호화 등 안전성 확보조치 수행</t>
         </is>
       </c>
       <c r="N178" s="3" t="inlineStr">
         <is>
-          <t>중(공식 조직명칭 검색 확인 + 알리오 기관정보)</t>
+          <t>상(공식 개인정보처리방침 + 공공데이터포털 담당부서 표기 + 알리오 교차 확인)</t>
         </is>
       </c>
       <c r="O178" s="3" t="inlineStr">
         <is>
-          <t>2022.1.28 한국보건복지인력개발원→한국보건복지인재원 명칭 변경. 보건·복지 교육훈련 전문기관. 정보화전략부가 정보화 총괄, 정보보안팀 별도 운영. 경영전략본부 등 본부 체계 하에 운영지원부·정보화전략부 편제(추정).</t>
+          <t>2022.1.28 한국보건복지인력개발원→한국보건복지인재원 명칭 변경. 보건·복지 교육훈련 전문기관(오송 소재). 경영전략본부 체계 하에 정보화전략부가 정보화·정보보안·개인정보·교육관리통합시스템을 총괄. 정보시스템 통합유지보수 위탁(㈜오파스넷). 개인정보 보호수준 평가 2022년 'S등급', 2023~2024년 'A등급'.</t>
         </is>
       </c>
     </row>
@@ -14021,17 +14021,17 @@
       </c>
       <c r="F181" s="3" t="inlineStr">
         <is>
-          <t>정보지원실 (연금사업본부 산하)</t>
+          <t>정보지원실·정보보안센터 (연금사업본부 산하)</t>
         </is>
       </c>
       <c r="G181" s="3" t="inlineStr">
         <is>
-          <t>실(본부 산하)</t>
+          <t>실·센터(본부 산하)</t>
         </is>
       </c>
       <c r="H181" s="3" t="inlineStr">
         <is>
-          <t>정보지원실(전산운영팀, 정보보안팀)</t>
+          <t>정보지원실(전산운영), 정보보안센터(정보보안·개인정보)</t>
         </is>
       </c>
       <c r="I181" s="3" t="inlineStr">
@@ -14041,7 +14041,7 @@
       </c>
       <c r="J181" s="3" t="inlineStr">
         <is>
-          <t>확인불가 (별도 AI 전담부서 미확인)</t>
+          <t>확인불가 (별도 AI 전담부서 미확인. AX·DX 경영혁신·AI 혁신보드·AI 자문위원 'T-쌤' 운영 — 조직 직제 아님)</t>
         </is>
       </c>
       <c r="K181" s="3" t="inlineStr">
@@ -14051,22 +14051,22 @@
       </c>
       <c r="L181" s="3" t="inlineStr">
         <is>
-          <t>확인불가 (정보지원실 소관 연금사업본부장 겸임 추정)</t>
+          <t>확인불가 (정보지원실·정보보안센터 소관 연금사업본부장 겸임 추정). ※ 보도상 'CIO'는 자금운용관리단장(Chief Investment Officer, 투자책임자)을 지칭 — IT CIO와 별개</t>
         </is>
       </c>
       <c r="M181" s="3" t="inlineStr">
         <is>
-          <t>정보지원실 내 정보보안팀 운영(전담 CISO 직위 미확인). ISMS 인증 취득(2018)</t>
+          <t>개인정보보호책임자(CPO)=연금사업본부 정보보안센터장(김석). 정보보안센터가 정보보안·개인정보 총괄. ISMS 인증(2018), 개인정보 관리수준진단 'S'등급(2022), 정보보호 불시점검 등 운영. 별도 명시 CISO 직위는 미표기(정보보안센터장이 보안 총괄)</t>
         </is>
       </c>
       <c r="N181" s="3" t="inlineStr">
         <is>
-          <t>중(공식자료 기반 조직표 + 알리오, AI는 보도 보조)</t>
+          <t>상(공식 개인정보처리방침 + 알리오 + 보도 교차 확인)</t>
         </is>
       </c>
       <c r="O181" s="3" t="inlineStr">
         <is>
-          <t>1974년 설립, 나주 소재. 경영관리본부·연금사업본부·자금운용관리단·리스크관리실 체계. 정보화는 연금사업본부 산하 정보지원실(전산운영팀·정보보안팀)이 담당. 2024.7 공무원연금공단과 '디지털플랫폼정부' 구현 업무협약(AI·데이터 공유) 체결 — 전담 AI조직 신설과는 별개.</t>
+          <t>1974년 설립, 나주 소재. 경영관리본부·연금사업본부·자금운용관리단·리스크관리실 체계. 정보화는 연금사업본부 산하 정보지원실(전산운영)·정보보안센터(정보보안·개인정보)가 담당. 2026년 'AX·DX 기반 지능형 연금·복지 서비스 기관' 경영혁신 추진, 공공기관 최초 AI 혁신자문위원 'T-쌤' 위촉·AI 혁신보드 운영 — 전담 AI 조직 신설과는 별개의 거버넌스/자문 단위.</t>
         </is>
       </c>
     </row>
@@ -14246,17 +14246,17 @@
       </c>
       <c r="F184" s="3" t="inlineStr">
         <is>
-          <t>경영기획본부(정보화·정보보안 기능 포함)</t>
+          <t>인재운영처 (경영기획본부 산하) — 정보화·정보보안 기능 보유</t>
         </is>
       </c>
       <c r="G184" s="3" t="inlineStr">
         <is>
-          <t>처·실(본부 산하) (추정)</t>
+          <t>처(본부 산하)</t>
         </is>
       </c>
       <c r="H184" s="3" t="inlineStr">
         <is>
-          <t>확인불가 (경영기획본부 내 정보화/시스템운영/정보보안 담당 — 별도 IT 전담 처·팀 명칭 미확인)</t>
+          <t>정보안전팀 (인재운영처 소속, 정보화·정보보안·개인정보 담당)</t>
         </is>
       </c>
       <c r="I184" s="3" t="inlineStr">
@@ -14266,32 +14266,32 @@
       </c>
       <c r="J184" s="3" t="inlineStr">
         <is>
-          <t>(해당없음)</t>
+          <t>확인불가 (별도 AI 전담조직 미확인)</t>
         </is>
       </c>
       <c r="K184" s="3" t="inlineStr">
         <is>
-          <t>(해당없음)</t>
+          <t>확인불가</t>
         </is>
       </c>
       <c r="L184" s="3" t="inlineStr">
         <is>
-          <t>확인불가 (경영기획본부장 겸임 추정)</t>
+          <t>확인불가 (인재운영처장 소관 추정 — 개인정보보호책임자(CPO)도 인재운영처장(정재환))</t>
         </is>
       </c>
       <c r="M184" s="3" t="inlineStr">
         <is>
-          <t>확인불가</t>
+          <t>확인불가 (별도 CISO 직위 미표기). 개인정보보호책임자(CPO)=인재운영처장(정재환), 담당부서=인재운영처 정보안전팀. 정보안전팀이 정보보안·접근통제·암호화 등 안전성 확보조치 수행. 개인정보 보호수준 평가 'A'등급(2024)</t>
         </is>
       </c>
       <c r="N184" s="3" t="inlineStr">
         <is>
-          <t>중(공식 홈페이지 본부구조 + 채용공고 교차확인, IT 세부조직명 미달)</t>
+          <t>상(공식 조직도(텍스트 확인) + 공식 개인정보처리방침 교차 확인)</t>
         </is>
       </c>
       <c r="O184" s="3" t="inlineStr">
         <is>
-          <t>2023.12 환경보전협회를 모태로 '한국환경보전원(KECI)'으로 새 출범. 본부 구성: 경영기획본부, 환경사업본부, 환경생태본부, 국가환경교육센터 + 감사실. 공식 조직도가 이미지로 게시되어 IT 세부 부서명 직접 추출 불가. 2024~2025 채용공고에 '정보화', '정보보안', '시스템운영' 직무가 포함되어 정보화 기능 보유는 확인됨. 별도 IT 본부/처 신설 단서 없음.</t>
+          <t>2023.12 환경보전협회를 모태로 '한국환경보전원(KECI)'으로 새 출범(영문 Korea Environmental Conservation Institute). 조직: 원장 직속 감사실 + 4개 본부/센터(경영기획본부·환경사업본부·환경생태본부·국가환경교육센터) + 4개 지사. 경영기획본부 산하에 기획성과처·인재운영처가 있으며, IT/정보화·정보보안은 인재운영처 '정보안전팀'이 담당(인사운영팀과 병렬). 별도 IT 전담 본부/처는 없음.</t>
         </is>
       </c>
     </row>
@@ -14621,27 +14621,27 @@
       </c>
       <c r="F189" s="3" t="inlineStr">
         <is>
-          <t>확인불가(별도 IT 총괄 본부·처 미확인)</t>
+          <t>경영지원부 (경영본부 산하) — 정보화·정보보안·개인정보 기능 보유</t>
         </is>
       </c>
       <c r="G189" s="3" t="inlineStr">
         <is>
-          <t>팀(추정)</t>
+          <t>부(본부 산하)</t>
         </is>
       </c>
       <c r="H189" s="3" t="inlineStr">
         <is>
-          <t>정보화 담당부서(정보시스템 관리·정보보안·개인정보보호·항만물류 정보화 업무 수행, 부서명 확인불가)</t>
+          <t>경영지원부 (정보시스템 관리·정보보안·개인정보보호·항만물류 정보화 업무 수행)</t>
         </is>
       </c>
       <c r="I189" s="3" t="inlineStr">
         <is>
-          <t>없음(전담조직 미확인, 단 스마트항만 전담조직 신설)</t>
+          <t>없음 (전담 AI 조직 미확인. 스마트항만은 개발사업본부 산하 '자동화사업실'이 항만자동화(장비·터미널운영시스템) 담당 — 일반 IT/AI 전담조직과 별개)</t>
         </is>
       </c>
       <c r="J189" s="3" t="inlineStr">
         <is>
-          <t>확인불가(스마트항만 전담 조직 신설 — 명칭 확인불가)</t>
+          <t>확인불가 (별도 AI 전담조직 명칭 미확인)</t>
         </is>
       </c>
       <c r="K189" s="3" t="inlineStr">
@@ -14651,22 +14651,22 @@
       </c>
       <c r="L189" s="3" t="inlineStr">
         <is>
-          <t>확인불가</t>
+          <t>확인불가 (경영지원부 소관 경영본부장 겸임 추정)</t>
         </is>
       </c>
       <c r="M189" s="3" t="inlineStr">
         <is>
-          <t>확인불가</t>
+          <t>확인불가 (별도 CISO 직위 미표기). 개인정보보호책임자(CPO)=경영지원부장(박정철), 담당부서=경영지원부. ISMS/ePRIVACY plus 인증 7년 연속(2025-EP-R021), 안전성 확보조치 시행</t>
         </is>
       </c>
       <c r="N189" s="3" t="inlineStr">
         <is>
-          <t>중(공식 홈페이지 조직도 + 알리오플러스 1차, 단 IT 부서명 직접 확인 실패)</t>
+          <t>상(공식 조직도(2026-05-22, 텍스트 확인) + 공식 개인정보처리방침 교차 확인)</t>
         </is>
       </c>
       <c r="O189" s="3" t="inlineStr">
         <is>
-          <t>최근 조직개편(2본부 4실 9부 1사업소 → 2본부 1단 7실 6부 1지사)으로 스마트항만 전담조직 신설. 네이버클라우드와 'K-Smart AI 종합항만 전환' 협약 체결 등 AI·IoT 기반 스마트항만 추진 중. 사장 직속 혁신TF 운영.</t>
+          <t>2026.5 기준 조직(2본부 체계): 사장 직속(재난안전실·상생소통부·감사실·정책과제TF) + 경영본부(기획조정실·ESG경영실·경영지원부·재무회계부) + 운영본부(물류전략실·물류단지부·마케팅부·여수지사) + 개발사업본부(자동화사업실·항만개발부·항만시설부) + 여수엑스포사후활용추진단. 정보화·정보보안·개인정보는 경영본부 산하 경영지원부가 담당. 별도 IT 총괄 본부/처는 없음. 네이버클라우드와 'K-Smart AI 종합항만' 협약 등 AI·IoT 기반 스마트항만 추진(사업), 광양항 항만자동화 테스트베드 구축(자동화사업실).</t>
         </is>
       </c>
     </row>
@@ -14996,17 +14996,17 @@
       </c>
       <c r="F194" s="3" t="inlineStr">
         <is>
-          <t>융합기술센터</t>
+          <t>융합기술센터(방송기술·시스템) / 데이터정보화팀(데이터·정보화·개인정보)</t>
         </is>
       </c>
       <c r="G194" s="3" t="inlineStr">
         <is>
-          <t>센터(본부 산하) — 경영본부 산하 (2본부4센터8팀1반 체계)</t>
+          <t>센터·팀(경영본부 산하) — 2본부4센터8팀1반 체계</t>
         </is>
       </c>
       <c r="H194" s="3" t="inlineStr">
         <is>
-          <t>기술관리(방송 기술기획·시스템 매니지먼트 등), 방송정보화시스템 운영, 정보보안 관리</t>
+          <t>융합기술센터(방송정보화시스템 운영·네트워크 인프라·정보보안 관리), 데이터정보화팀(공공데이터·데이터기반행정·정보화·개인정보)</t>
         </is>
       </c>
       <c r="I194" s="3" t="inlineStr">
@@ -15016,7 +15016,7 @@
       </c>
       <c r="J194" s="3" t="inlineStr">
         <is>
-          <t>확인불가('AI데이터정보화센터' 명칭은 과거(2024년 무렵) 데이터·정보화 기능 표기로 추정, 2025 공시는 융합기술센터로 표기)</t>
+          <t>확인불가 (별도 AI 전담조직 미확인. 'AI데이터정보화센터'는 과거(2024) 명칭으로, 2025 공시는 융합기술센터/데이터정보화팀으로 정리됨)</t>
         </is>
       </c>
       <c r="K194" s="3" t="inlineStr">
@@ -15026,21 +15026,21 @@
       </c>
       <c r="L194" s="3" t="inlineStr">
         <is>
-          <t>확인불가(기술·정보화 총괄은 융합기술센터장)</t>
+          <t>확인불가 (기술·정보화 총괄은 융합기술센터장. 데이터·정보화·개인정보 소관 본부는 경영본부)</t>
         </is>
       </c>
       <c r="M194" s="3" t="inlineStr">
         <is>
-          <t>확인불가(방송정보화시스템 정보보안 관리체계 운영 — 융합기술센터 담당)</t>
+          <t>확인불가 (별도 CISO 직위 미표기). 개인정보보호책임자(CPO)=경영본부장(직무대행 홍종호), 담당부서=데이터정보화팀(이성일). 방송정보화시스템 정보보안 관리체계는 융합기술센터가 운영. 개인정보 관리수준진단 'A'등급(2024)</t>
         </is>
       </c>
       <c r="N194" s="3" t="inlineStr">
         <is>
-          <t>중(공식 공시자료(2024·2025 부서별 업무추진계획) + 보도자료 교차, 단 2026 현행 조직도 텍스트 직접 미확인)</t>
+          <t>상(공식 개인정보처리방침(2025.7.10) + 공시 부서별 업무추진계획 + 보도 교차 확인)</t>
         </is>
       </c>
       <c r="O194" s="3">
-        <f>아리랑국제방송(아리랑TV). 자회사 아리랑TV미디어 보유. 2024→2025 조직개편: 기존 2본부12센터1반 → 2본부4센터8팀1반으로 축소. 기술·정보화·정보보안은 '융합기술센터'가 총괄(방송정보화시스템 구축·유지보수, 네트워크 인프라, 정보보안 관리체계). 데이터기반행정·공공데이터·홈페이지 인프라 기능은 과거 'AI데이터정보화센터'로 소개된 바 있으나 2025 공시 기준 명칭 변동.</f>
+        <f>아리랑국제방송(아리랑TV/KIBF). 자회사 아리랑TV미디어 보유. 2024→2025 조직개편: 기존 2본부12센터1반 → 2본부4센터8팀1반으로 축소. 방송기술·방송정보화시스템·네트워크·정보보안은 '융합기술센터'가 총괄. 데이터기반행정·공공데이터·정보화·개인정보 실무는 경영본부 산하 '데이터정보화팀'이 담당.</f>
         <v/>
       </c>
     </row>
@@ -15520,17 +15520,17 @@
       </c>
       <c r="F201" s="3" t="inlineStr">
         <is>
-          <t>지능정보부 (경영관리본부 산하, 추정)</t>
+          <t>전략기획실 (정보화·정보보안·개인정보보호 총괄, 산하 지능정보부 담당)</t>
         </is>
       </c>
       <c r="G201" s="3" t="inlineStr">
         <is>
-          <t>부(본부 산하)</t>
+          <t>처·실(본부 산하 아님 — 관장 직속 전략기획실 산하 부)</t>
         </is>
       </c>
       <c r="H201" s="3" t="inlineStr">
         <is>
-          <t>확인불가 (부 단위, 별도 하위팀 미확인)</t>
+          <t>지능정보부 (전략기획실 산하, 기관 정보화·정보보안·개인정보보호 총괄)</t>
         </is>
       </c>
       <c r="I201" s="3" t="inlineStr">
@@ -15550,22 +15550,22 @@
       </c>
       <c r="L201" s="3" t="inlineStr">
         <is>
-          <t>확인불가 (경영관리본부장 겸임 추정)</t>
+          <t>전략기획실장 총괄 (개인정보보호 실무 총괄 — 전략기획실장 도기용, 보도 인용 기준)</t>
         </is>
       </c>
       <c r="M201" s="3" t="inlineStr">
         <is>
-          <t>확인불가</t>
+          <t>전략기획실 지능정보부 겸장 (정보보안·개인정보보호 담당)</t>
         </is>
       </c>
       <c r="N201" s="3" t="inlineStr">
         <is>
-          <t>중(공식 1출처 + 공공데이터포털)</t>
+          <t>상(공식 조직페이지 + 보안뉴스 + 플랫폼 개인정보처리방침)</t>
         </is>
       </c>
       <c r="O201" s="3" t="inlineStr">
         <is>
-          <t>담수생물 전문 연구기관. 정보화 기능은 경영관리본부 내 '지능정보부'가 담당(공공데이터포털 조직정보 관리부서 기준, 2026-05-12). 별도 AI 전담조직은 없으나 담수생물 데이터 관리·디지털이미지 전환·AI 종판별 등 연구 차원의 디지털 활용은 수행. 조직은 경영관리본부(전략기획실·경영관리실·전시교육실) + 담수생물연구본부 체계.</t>
+          <t>담수생물 전문 연구기관. 정보화 기능은 관장 직속 '전략기획실' 산하 '지능정보부'가 담당하며, 기관 정보화·정보보안·개인정보보호 업무를 총괄(보안뉴스 2024 개인정보보호 우수사례 및 공식 조직페이지 확인). 2025년 개인정보 보호수준 평가 'S'등급. 별도 AI 전담조직은 없으나 담수생물 데이터 관리·디지털이미지 전환·AI 종판별 등 연구 차원의 디지털 활용은 수행. 조직은 전략기획실(기획부·성과혁신부·지능정보부) + 경영관리본부(경영관리실·전시교육실) + 담수생물연구본부 체계.</t>
         </is>
       </c>
     </row>
@@ -16055,42 +16055,42 @@
       </c>
       <c r="H208" s="3" t="inlineStr">
         <is>
-          <t>스마트농업실, 정보전략실 (그 외 데이터·정보화 관련 실 포함, 일부 확인불가)</t>
+          <t>스마트농업기획실 (현 공식 개인정보처리방침 확인), 데이터분석실·디지털농정실(조직개편 보도 기준), 스마트농업지원단(스마트팜확산실)</t>
         </is>
       </c>
       <c r="I208" s="3" t="inlineStr">
         <is>
-          <t>확인불가 (AI 전담 명칭 조직은 미확인, 디지털혁신본부 내 스마트농업/데이터 기능에 AI 포함 추정)</t>
+          <t>없음 (별도 'AI' 명칭 전담조직 미확인 — AI 사업은 디지털혁신본부/스마트농업 기능에서 추진)</t>
         </is>
       </c>
       <c r="J208" s="3" t="inlineStr">
         <is>
-          <t>확인불가</t>
+          <t>해당없음 (전담조직 부재)</t>
         </is>
       </c>
       <c r="K208" s="3" t="inlineStr">
         <is>
-          <t>확인불가</t>
+          <t>해당없음</t>
         </is>
       </c>
       <c r="L208" s="3" t="inlineStr">
         <is>
-          <t>확인불가 (디지털혁신본부장이 정보화 총괄로 추정)</t>
+          <t>디지털혁신본부장 (개인정보보호책임자(CPO) 겸임 — 디지털혁신본부 본부장직무대리 이규술, 2025.12 기준)</t>
         </is>
       </c>
       <c r="M208" s="3" t="inlineStr">
         <is>
-          <t>확인불가 (정보전략실이 정보보호 담당으로 추정)</t>
+          <t>디지털혁신본부 겸장 (개인정보보호 실무 담당: 스마트농업기획실). 별도 CISO 직위 미표기</t>
         </is>
       </c>
       <c r="N208" s="3" t="inlineStr">
         <is>
-          <t>중(공식 1출처 + 간접 2출처)</t>
+          <t>상(공식 개인정보처리방침 + 조직개편 보도 + AI 사업 다출처)</t>
         </is>
       </c>
       <c r="O208" s="3" t="inlineStr">
         <is>
-          <t>약칭 '농정원'(EPIS). 기관 자체가 농식품·농촌 정보화 촉진을 설립 목적으로 하는 정보화 전문기관. '디지털혁신본부' 산하 '스마트농업실'이 스마트팜·빅데이터·AI 기반 농업 사업 추진. 공공데이터포털상 데이터 관리부서로 '정보전략실' 표기. 4본부 체계 기반 조직개편 이력 보유.</t>
+          <t>약칭 '농정원'(EPIS). 기관 자체가 농식품·농촌 정보화 촉진을 설립 목적으로 하는 정보화 전문기관. '디지털혁신본부'가 IT/디지털 총괄. **2026.5 과기정통부 '국가 인공지능 프로젝트'에 선정되어 고성능 GPU 32장 확보(공공 16·민간 16) → 농가 작물 생육 사진·영상을 AI 모델로 판독·분석, 학습용 데이터·스마트팜 데이터 자동추출 서비스 추진** 등 AI 사업을 적극 추진하나, 'AI' 명칭의 상설 전담조직은 미확인. 디지털혁신본부 산하 개인정보보호 실무는 '스마트농업기획실'이 담당. 정부 공공기관 혁신 가이드라인에 따른 조직 축소 개편 이력 보유(4개 단위조직 축소).</t>
         </is>
       </c>
     </row>
@@ -16270,17 +16270,17 @@
       </c>
       <c r="F211" s="3" t="inlineStr">
         <is>
-          <t>경영관리본부 (정보화·전산 기능 포함, 별도 IT 전담 처·실 없음)</t>
+          <t>전략기획실 (정보화·정보보안·개인정보보호 담당, 산하 정보관리부)</t>
         </is>
       </c>
       <c r="G211" s="3" t="inlineStr">
         <is>
-          <t>본부 산하 (전담 IT 실·부 없이 경영관리 기능 내 포함)</t>
+          <t>처·실(본부 산하 아님 — 관장 직속 전략기획실 산하 부)</t>
         </is>
       </c>
       <c r="H211" s="3" t="inlineStr">
         <is>
-          <t>확인불가 (경영관리본부 내 정보화/전산 담당, 별도 정보화팀 명칭 미확인)</t>
+          <t>정보관리부 (전략기획실 산하, 정보화·정보보안·개인정보보호 담당)</t>
         </is>
       </c>
       <c r="I211" s="3" t="inlineStr">
@@ -16300,22 +16300,22 @@
       </c>
       <c r="L211" s="3" t="inlineStr">
         <is>
-          <t>확인불가</t>
+          <t>확인불가 (전략기획실장 총괄 추정)</t>
         </is>
       </c>
       <c r="M211" s="3" t="inlineStr">
         <is>
-          <t>확인불가</t>
+          <t>정보관리부 겸장 (정보화·정보보안·개인정보보호 담당). 개인정보보호책임자(CPO)는 관장(박진영)으로 격상</t>
         </is>
       </c>
       <c r="N211" s="3" t="inlineStr">
         <is>
-          <t>중(공식 1출처 + 보도·간접 2출처)</t>
+          <t>상(공식 개인정보처리방침 + 공식 직원검색 + 보도 2출처)</t>
         </is>
       </c>
       <c r="O211" s="3" t="inlineStr">
         <is>
-          <t>약칭 HNIBR. 2020년 설립·2021년 개관한 소규모 연구기관(임직원 약 184명). 조직은 크게 2개 본부(경영관리본부, 도서생물연구본부)와 6개 실 체계로 운영. 정보화·전산은 경영관리본부 내 기능으로 수행하며 별도 정보화처/실은 미확인. 생물표본·자원 '디지털전환' 사업(고해상도 표본 디지털이미지화 등)은 추진 중이나 이는 연구 데이터 사업이며 IT 전담조직과는 별개. 직원검색상 '디지털화 담당' 직무 표기 존재.</t>
+          <t>약칭 HNIBR. 2020년 설립·2021년 개관한 소규모 연구기관. 조직은 전략기획실(기획성과부·전략홍보부 등) + 경영관리본부(경영관리실·전시교육실) 등 2개 본부·6개 실 체계. 정보화·정보보안·개인정보보호는 전략기획실 산하 '정보관리부'가 담당(공식 개인정보처리방침 확인). 개인정보보호 평가에서 보호책임자를 부장→기관장으로 격상하고 개인정보보호협의회를 구성·운영. 생물표본·자원 '디지털전환' 사업은 추진 중이나 이는 연구 데이터 사업으로 IT 전담조직과는 별개.</t>
         </is>
       </c>
     </row>
@@ -16495,22 +16495,22 @@
       </c>
       <c r="F214" s="3" t="inlineStr">
         <is>
-          <t>확인불가 (행정조직 '1부·1실·1과' 체제 — 별도 정보화 본부·처·실 없음. 전산·정보화는 행정부 또는 기획조정실 산하 기능으로 수행)</t>
+          <t>사무국 (행정 '1부·1실·1과' 체제 — 별도 정보화 본부·처·실 없음. 전산·정보화·의료정보는 사무국 행정기능으로 수행)</t>
         </is>
       </c>
       <c r="G214" s="3" t="inlineStr">
         <is>
-          <t>팀 이하 (별도 IT 조직 단위 없음 — 행정부서 내 담당)</t>
+          <t>팀 이하 (별도 IT 조직 단위 없음 — 사무국 행정부서 내 담당)</t>
         </is>
       </c>
       <c r="H214" s="3" t="inlineStr">
         <is>
-          <t>확인불가 (전산·정보화 전담 부서명 미확인 / 행정부 내 전산 담당 추정)</t>
+          <t>확인불가 (전산·정보화 전담 부서명 미확인 / 사무국 내 행정·원무팀이 의료정보시스템·개인정보 업무 겸장 추정)</t>
         </is>
       </c>
       <c r="I214" s="3" t="inlineStr">
         <is>
-          <t>없음 (확인불가에 가까움 — 별도 AI 조직 단서 미확인)</t>
+          <t>없음 (별도 AI 조직 단서 미확인)</t>
         </is>
       </c>
       <c r="J214" s="3" t="inlineStr">
@@ -16525,22 +16525,22 @@
       </c>
       <c r="L214" s="3" t="inlineStr">
         <is>
-          <t>확인불가 (사무국장/기획조정실장 총괄 추정)</t>
+          <t>확인불가 (사무국장 총괄 추정)</t>
         </is>
       </c>
       <c r="M214" s="3" t="inlineStr">
         <is>
-          <t>확인불가 (의료정보·환자정보 보안 업무는 존재하나 전담 CISO 직위 미확인)</t>
+          <t>개인정보보호책임자(CPO) 별도 지정 운영 (치주과 소속 임원급, 연락처 033-640-3199 / periojk@gwnu.ac.kr). 개인정보보호 담당부서(033-640-3111) 및 열람청구 담당 원무팀(033-640-3115) 운영. 정보보안 시스템(PACS·EDR·ERP·DB암호화·NAC 등)은 위탁 운영. 전담 CISO 직위 명칭은 미확인</t>
         </is>
       </c>
       <c r="N214" s="3" t="inlineStr">
         <is>
-          <t>중(국회 업무보고·홈페이지 등으로 행정조직 체제 확인, 전산 전담부서명 미확정)</t>
+          <t>중(공식 개인정보처리방침·전화번호안내·국회 업무보고로 CPO·행정체제 확인, 전산 전담부서명 미확정)</t>
         </is>
       </c>
       <c r="O214" s="3" t="inlineStr">
         <is>
-          <t>강릉 소재 국립대치과병원(교육부 산하, 「국립대학치과병원설치법」에 따른 독립 특수법인). 행정조직은 '1부·1실·1과' 체제(국회 교육위 업무보고 기준)로 기획조정실 보유. 소규모 기관(약 161명)으로 별도 정보화 본부·처·실 없이 행정부서가 전산·정보화·의료정보시스템(PACS 등) 업무를 겸장. 영문명 Gangneung-Wonju National University Dental Hospital(전신 강릉대학교치과병원). 강원대학교 본교 '정보화본부'는 별개 법인의 IT조직이므로 혼동 금지.</t>
+          <t>강릉 소재 국립대치과병원(교육부 산하, 「국립대학치과병원설치법」에 따른 독립 특수법인). 공식 도메인 knudh.or.kr(이메일 gwnudh.or.kr)로, 강릉원주대학교치과병원이 강원대-강릉원주대 통합(2024~2025)에 따라 '강원대학교치과병원'으로 운영. 행정조직은 '1부·1실·1과' 체제(국회 교육위 업무보고 기준)로 기획조정실 보유. 소규모 기관(약 161명)으로 별도 정보화 본부·처·실 없이 사무국 행정부서가 전산·정보화·의료정보시스템(PACS 등)·개인정보보호 업무를 겸장. 개인정보보호책임자(CPO)는 별도 지정·운영. 강원대학교 본교 '정보화본부'는 별개 법인의 IT조직이므로 혼동 금지.</t>
         </is>
       </c>
     </row>
@@ -16580,12 +16580,12 @@
       </c>
       <c r="H215" s="3" t="inlineStr">
         <is>
-          <t>전산정보화팀 (디지털 인프라·정보시스템 운영)</t>
+          <t>전산정보화팀 (경영정보시스템·디지털 인프라·정보시스템 운영)</t>
         </is>
       </c>
       <c r="I215" s="3" t="inlineStr">
         <is>
-          <t>없음 (확인불가에 가까움 — 별도 AI 전담 조직 미확인)</t>
+          <t>없음 (공식 조직도상 AI 전담 상설조직 미확인 — AI는 사업 형태로 추진)</t>
         </is>
       </c>
       <c r="J215" s="3" t="inlineStr">
@@ -16600,22 +16600,22 @@
       </c>
       <c r="L215" s="3" t="inlineStr">
         <is>
-          <t>확인불가 (기획조정본부장 총괄 추정)</t>
+          <t>기획조정본부장 총괄 (전산정보화팀 소관 본부장, 추정)</t>
         </is>
       </c>
       <c r="M215" s="3" t="inlineStr">
         <is>
-          <t>확인불가 (전산정보화팀 내 수행 추정)</t>
+          <t>경영지원본부장 겸임 (개인정보보호책임자(CPO)=경영지원본부장 손주영, 실무 담당 안전관리팀). 전산정보화팀은 경영정보시스템 운영 담당</t>
         </is>
       </c>
       <c r="N215" s="3" t="inlineStr">
         <is>
-          <t>중(공식 1출처)</t>
+          <t>상(공식 조직도 + 공식 개인정보처리방침)</t>
         </is>
       </c>
       <c r="O215" s="3" t="inlineStr">
         <is>
-          <t>IT 기능은 기획조정본부 산하 '전산정보화팀'에 집중. 별도 AI 전담조직이나 CISO 전담 부서는 공식 조직도에 명시되지 않음. 다만 'INNOPOLIS+ AI 초고속 기술·산업 연계 플랫폼', 'AI 글로벌 빅테크 육성사업' 등 AI 관련 사업은 특구육성/사업화 부서에서 사업 형태로 추진(전담조직 아님).</t>
+          <t>IT 기능은 기획조정본부 산하 '전산정보화팀'에 집중(경영정보시스템 운영). 개인정보보호책임자(CPO)는 경영지원본부장이 겸임하며 실무는 안전관리팀(경영지원본부)이 담당 → IT 운영(기획조정본부)과 정보보호 거버넌스(경영지원본부)가 분리. 별도 AI 전담 상설조직은 공식 조직도에 없음. 다만 'INNOPOLIS+ AI 초고속 기술·산업 연계 플랫폼', 'AI 글로벌 빅테크 육성사업' 등 AI 관련 사업은 특구육성/사업부서에서 사업 형태로 추진(전담조직 아님). 2025년 웹어워드코리아 공공기관분야 대상.</t>
         </is>
       </c>
     </row>
@@ -16720,7 +16720,7 @@
       </c>
       <c r="F217" s="3" t="inlineStr">
         <is>
-          <t>안전관리부 (정보보안·개인정보보호·전산 포함)</t>
+          <t>안전경영부 (정보화·정보보안·개인정보보호 포함, 별도 IT 전담 부서 없음)</t>
         </is>
       </c>
       <c r="G217" s="3" t="inlineStr">
@@ -16730,7 +16730,7 @@
       </c>
       <c r="H217" s="3" t="inlineStr">
         <is>
-          <t>확인불가 (안전관리부가 인사·회계·구매와 함께 정보보안·개인정보보호 겸장)</t>
+          <t>안전경영부 (인사·보수·노무·구매·계약·회계와 함께 정보화·정보보안·개인정보보호·행정정보 공동이용 겸장 / 별도 정보화팀 없음)</t>
         </is>
       </c>
       <c r="I217" s="3" t="inlineStr">
@@ -16750,22 +16750,22 @@
       </c>
       <c r="L217" s="3" t="inlineStr">
         <is>
-          <t>확인불가 (사무총장/안전관리부장 총괄 추정)</t>
+          <t>사무총장 총괄 (개인정보보호책임자(CPO)=사무총장 이주태)</t>
         </is>
       </c>
       <c r="M217" s="3" t="inlineStr">
         <is>
-          <t>안전관리부 겸장 (정보보안·개인정보보호 담당)</t>
+          <t>안전경영부 겸장 (정보화·정보보안·개인정보보호 담당, 개인정보 보호담당자 안전경영부 이유진)</t>
         </is>
       </c>
       <c r="N217" s="3" t="inlineStr">
         <is>
-          <t>중(공식 1출처)</t>
+          <t>상(공식 조직도 + 공식 개인정보처리방침)</t>
         </is>
       </c>
       <c r="O217" s="3" t="inlineStr">
         <is>
-          <t>대외명칭 '남북하나재단'. 별도 정보화/IT 전담 부서가 없으며, 정보보안·개인정보보호 기능이 '안전관리부'(인사·회계·구매와 통합)에 포함. AI 전담조직 없음. 조직 규모상 IT는 행정지원 기능의 일부로 운영.</t>
+          <t>대외명칭 '남북하나재단'. 별도 정보화/IT 전담 부서가 없으며, 정보화·정보보안·개인정보보호 기능이 '안전경영부'(인사·보수·노무·구매·계약·회계와 통합)에 포함. 개인정보보호책임자(CPO)는 사무총장이 겸임. AI 전담조직 없음. 조직 규모상 IT는 행정지원 기능의 일부로 운영. 현 조직: 이사장-사무총장 산하 전략기획실·대외협력실·안전경영부·사회적응부·일자리지원부·교육지원부 + 감사윤리팀(독립).</t>
         </is>
       </c>
     </row>
@@ -21280,19 +21280,19 @@
         </is>
       </c>
       <c r="E5" s="5" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>35.3%</t>
+          <t>35.9%</t>
         </is>
       </c>
       <c r="G5" s="5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H5" s="5" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>4.9%</t>
         </is>
       </c>
     </row>
@@ -21314,19 +21314,19 @@
         </is>
       </c>
       <c r="E6" s="5" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>49.3%</t>
+          <t>49.6%</t>
         </is>
       </c>
       <c r="G6" s="5" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H6" s="5" t="inlineStr">
         <is>
-          <t>9.1%</t>
+          <t>9.5%</t>
         </is>
       </c>
     </row>
@@ -21383,11 +21383,11 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>50.7%</t>
+          <t>51.5%</t>
         </is>
       </c>
     </row>
@@ -21398,11 +21398,11 @@
         </is>
       </c>
       <c r="B12" s="5" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>26.3%</t>
+          <t>25.9%</t>
         </is>
       </c>
     </row>
@@ -21413,11 +21413,11 @@
         </is>
       </c>
       <c r="B13" s="5" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>9.1%</t>
+          <t>8.8%</t>
         </is>
       </c>
     </row>
@@ -21459,11 +21459,11 @@
         </is>
       </c>
       <c r="B17" s="5" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>49.3%</t>
+          <t>49.6%</t>
         </is>
       </c>
     </row>
@@ -21474,11 +21474,11 @@
         </is>
       </c>
       <c r="B18" s="5" t="n">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>41.2%</t>
+          <t>41.6%</t>
         </is>
       </c>
     </row>
@@ -21489,11 +21489,11 @@
         </is>
       </c>
       <c r="B19" s="5" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>9.5%</t>
+          <t>8.8%</t>
         </is>
       </c>
     </row>
@@ -21535,11 +21535,11 @@
         </is>
       </c>
       <c r="B23" s="5" t="n">
-        <v>190</v>
+        <v>206</v>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>69.3%</t>
+          <t>75.2%</t>
         </is>
       </c>
     </row>
@@ -21550,11 +21550,11 @@
         </is>
       </c>
       <c r="B24" s="5" t="n">
-        <v>84</v>
+        <v>68</v>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>30.7%</t>
+          <t>24.8%</t>
         </is>
       </c>
     </row>
@@ -21599,7 +21599,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H36"/>
+  <dimension ref="A1:H31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -22264,7 +22264,7 @@
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>부산대학교치과병원</t>
+          <t>한국청소년상담복지개발원</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
@@ -22278,33 +22278,33 @@
         </is>
       </c>
       <c r="D18" s="3" t="n">
-        <v>255</v>
+        <v>239.5</v>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>중 (층별안내 등으로 '전산실' 존재 확인, 다만 조직도 트리·소속 라인은 이미지로만 제공되어 정확한 소속 미확정)</t>
+          <t>상(공식 조직 명칭 + 개인정보처리방침(공식) 교차 확인)</t>
         </is>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t>IT최상위 확인불가</t>
+          <t>AI전담 확인불가</t>
         </is>
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>확인불가 (별도 정보화 본부·처 없음 / '전산실'이 행정 단위로 존재 — 기획조정실·행정실과 동일 층(5F)에 배치, 기획조정실 또는 행정실 산하 운영 추정)</t>
+          <t>정보화전략부</t>
         </is>
       </c>
       <c r="H18" s="3" t="inlineStr">
         <is>
-          <t>없음 (조직 차원 AI 전담부서 미확인)</t>
+          <t>확인불가</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>한국식품안전관리인증원</t>
+          <t>한국보건복지인재원</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -22318,11 +22318,11 @@
         </is>
       </c>
       <c r="D19" s="3" t="n">
-        <v>241</v>
+        <v>238.6</v>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>중(공식성 보조 출처 1 + 보도 보조)</t>
+          <t>상(공식 개인정보처리방침 + 공공데이터포털 담당부서 표기 + 알리오 교차 확인)</t>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr">
@@ -22332,7 +22332,7 @@
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>기술혁신본부</t>
+          <t>정보화전략부 (경영전략본부 산하)</t>
         </is>
       </c>
       <c r="H19" s="3" t="inlineStr">
@@ -22344,7 +22344,7 @@
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>한국청소년상담복지개발원</t>
+          <t>사립학교교직원연금공단</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
@@ -22358,11 +22358,11 @@
         </is>
       </c>
       <c r="D20" s="3" t="n">
-        <v>239.5</v>
+        <v>232.5</v>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>중(공식 조직 명칭 1출처 + 보조 출처)</t>
+          <t>상(공식 개인정보처리방침 + 알리오 + 보도 교차 확인)</t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
@@ -22372,7 +22372,7 @@
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>정보화전략부</t>
+          <t>정보지원실·정보보안센터 (연금사업본부 산하)</t>
         </is>
       </c>
       <c r="H20" s="3" t="inlineStr">
@@ -22384,7 +22384,7 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>한국보건복지인재원</t>
+          <t>한국환경보전원</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
@@ -22398,11 +22398,11 @@
         </is>
       </c>
       <c r="D21" s="3" t="n">
-        <v>238.6</v>
+        <v>225</v>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>중(공식 조직명칭 검색 확인 + 알리오 기관정보)</t>
+          <t>상(공식 조직도(텍스트 확인) + 공식 개인정보처리방침 교차 확인)</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
@@ -22412,7 +22412,7 @@
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>정보화전략부</t>
+          <t>인재운영처 (경영기획본부 산하) — 정보화·정보보안 기능 보유</t>
         </is>
       </c>
       <c r="H21" s="3" t="inlineStr">
@@ -22424,7 +22424,7 @@
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>사립학교교직원연금공단</t>
+          <t>국제방송교류재단</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
@@ -22438,11 +22438,11 @@
         </is>
       </c>
       <c r="D22" s="3" t="n">
-        <v>232.5</v>
+        <v>202.3</v>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>중(공식자료 기반 조직표 + 알리오, AI는 보도 보조)</t>
+          <t>상(공식 개인정보처리방침(2025.7.10) + 공시 부서별 업무추진계획 + 보도 교차 확인)</t>
         </is>
       </c>
       <c r="F22" s="3" t="inlineStr">
@@ -22452,7 +22452,7 @@
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>정보지원실 (연금사업본부 산하)</t>
+          <t>융합기술센터(방송기술·시스템) / 데이터정보화팀(데이터·정보화·개인정보)</t>
         </is>
       </c>
       <c r="H22" s="3" t="inlineStr">
@@ -22464,7 +22464,7 @@
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>한국환경보전원</t>
+          <t>과학기술정책연구원</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
@@ -22478,11 +22478,11 @@
         </is>
       </c>
       <c r="D23" s="3" t="n">
-        <v>225</v>
+        <v>152</v>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>중(공식 홈페이지 본부구조 + 채용공고 교차확인, IT 세부조직명 미달)</t>
+          <t>중(공식 홈페이지 조직도 이미지 + 2026 개편 보도 다수 교차확인, 단 정확한 소속 라인 이미지 미파싱)</t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr">
@@ -22492,19 +22492,19 @@
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>경영기획본부(정보화·정보보안 기능 포함)</t>
+          <t>디지털전환팀(DAX팀) — 행정·경영지원 라인 소속 (추정)</t>
         </is>
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
-          <t>확인불가</t>
+          <t>확인불가 (전담 AI 조직 미확인 — 디지털·AI 전환 대응은 디지털전환팀이 수행)</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>여수광양항만공사</t>
+          <t>한국기상산업기술원</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -22518,33 +22518,33 @@
         </is>
       </c>
       <c r="D24" s="3" t="n">
-        <v>210</v>
+        <v>151.8</v>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>중(공식 홈페이지 조직도 + 알리오플러스 1차, 단 IT 부서명 직접 확인 실패)</t>
+          <t>상(공식 홈페이지 조직도 + 공공데이터포털 기관조직 데이터 교차확인)</t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t>IT최상위 확인불가</t>
+          <t>AI전담 확인불가</t>
         </is>
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>확인불가(별도 IT 총괄 본부·처 미확인)</t>
+          <t>경영지원실 (경영기획본부 소속) — 정보화·정보보안 기능 수행. 별도 IT 전담 본부·처 없음</t>
         </is>
       </c>
       <c r="H24" s="3" t="inlineStr">
         <is>
-          <t>없음(전담조직 미확인, 단 스마트항만 전담조직 신설)</t>
+          <t>확인불가 (전담 조직 미확인 — 데이터/AI 업무는 산업육성실 기상기후데이터·빅데이터 사업에서 수행)</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>국제방송교류재단</t>
+          <t>국립대구과학관</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
@@ -22558,33 +22558,33 @@
         </is>
       </c>
       <c r="D25" s="3" t="n">
-        <v>202.3</v>
+        <v>147</v>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>중(공식 공시자료(2024·2025 부서별 업무추진계획) + 보도자료 교차, 단 2026 현행 조직도 텍스트 직접 미확인)</t>
+          <t>중(실 단위 조직명은 보도·인사자료로 확인, 전산 전담부서명·소속은 미확정)</t>
         </is>
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t>AI전담 확인불가</t>
+          <t>IT최상위 확인불가 / AI전담 확인불가</t>
         </is>
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>융합기술센터</t>
+          <t>확인불가 (별도 IT 본부·처·실 없음 — 실 단위 조직 중 '경영관리실'이 전산·정보화 행정을 겸장하는 것으로 추정)</t>
         </is>
       </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
-          <t>확인불가</t>
+          <t>확인불가 (전담조직 미확인)</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>농림수산식품교육문화정보원</t>
+          <t>한국로봇산업진흥원</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
@@ -22598,33 +22598,33 @@
         </is>
       </c>
       <c r="D26" s="3" t="n">
-        <v>171.5</v>
+        <v>117</v>
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>중(공식 1출처 + 간접 2출처)</t>
+          <t>중(공식 홈페이지 도메인 확정 + 2026.5 개편 보도 교차, 내부 정보화 조직 직제는 미확인)</t>
         </is>
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t>AI전담 확인불가</t>
+          <t>IT최상위 확인불가</t>
         </is>
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>디지털혁신본부</t>
+          <t>확인불가 (별도 정보화 본부·실 없음 — 2본부 2실 체제, 정보화는 경영기획실 산하 기능으로 추정)</t>
         </is>
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
-          <t>확인불가 (AI 전담 명칭 조직은 미확인, 디지털혁신본부 내 스마트농업/데이터 기능에 AI 포함 추정)</t>
+          <t>있음(AX 본부 형태 — 단, AI 기술전담이 아닌 로봇산업진흥 본부)</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>강원대학교치과병원</t>
+          <t>한국여성정책연구원</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
@@ -22638,11 +22638,11 @@
         </is>
       </c>
       <c r="D27" s="3" t="n">
-        <v>161</v>
+        <v>116</v>
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t>중(국회 업무보고·홈페이지 등으로 행정조직 체제 확인, 전산 전담부서명 미확정)</t>
+          <t>중(공식 1출처 + 위키 보조 / IT·AI 세부조직 확인불가)</t>
         </is>
       </c>
       <c r="F27" s="3" t="inlineStr">
@@ -22652,19 +22652,19 @@
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>확인불가 (행정조직 '1부·1실·1과' 체제 — 별도 정보화 본부·처·실 없음. 전산·정보화는 행정부 또는 기획조정실 산하 기능으로 수행)</t>
+          <t>확인불가 (경영지원본부 산하 추정)</t>
         </is>
       </c>
       <c r="H27" s="3" t="inlineStr">
         <is>
-          <t>없음 (확인불가에 가까움 — 별도 AI 조직 단서 미확인)</t>
+          <t>없음 (확인불가에 가까움 — 별도 AI조직 단서 없음)</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>과학기술정책연구원</t>
+          <t>국립인천해양박물관</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
@@ -22678,33 +22678,33 @@
         </is>
       </c>
       <c r="D28" s="3" t="n">
-        <v>152</v>
+        <v>105</v>
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t>중(공식 홈페이지 조직도 이미지 + 2026 개편 보도 다수 교차확인, 단 정확한 소속 라인 이미지 미파싱)</t>
+          <t>중(공식 홈페이지 메뉴구조 확인, 상세 조직도는 JS 렌더링으로 부서 세부 미확정)</t>
         </is>
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t>AI전담 확인불가</t>
+          <t>IT최상위 확인불가</t>
         </is>
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>디지털전환팀(DAX팀) — 행정·경영지원 라인 소속 (추정)</t>
+          <t>확인불가 (정보화·전산 전담조직 식별 안 됨 — 신설 소규모 박물관, 경영지원실 내 총무 기능에 포함 추정)</t>
         </is>
       </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
-          <t>확인불가 (전담 AI 조직 미확인 — 디지털·AI 전환 대응은 디지털전환팀이 수행)</t>
+          <t>없음</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>한국기상산업기술원</t>
+          <t>한국저작권보호원</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
@@ -22718,11 +22718,11 @@
         </is>
       </c>
       <c r="D29" s="3" t="n">
-        <v>151.8</v>
+        <v>104.8</v>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>상(공식 홈페이지 조직도 + 공공데이터포털 기관조직 데이터 교차확인)</t>
+          <t>상(공식 홈페이지 조직도 + 공공데이터포털 관리부서 표기 교차확인)</t>
         </is>
       </c>
       <c r="F29" s="3" t="inlineStr">
@@ -22732,19 +22732,19 @@
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>경영지원실 (경영기획본부 소속) — 정보화·정보보안 기능 수행. 별도 IT 전담 본부·처 없음</t>
+          <t>정보기술부</t>
         </is>
       </c>
       <c r="H29" s="3" t="inlineStr">
         <is>
-          <t>확인불가 (전담 조직 미확인 — 데이터/AI 업무는 산업육성실 기상기후데이터·빅데이터 사업에서 수행)</t>
+          <t>확인불가 (별도 AI 전담조직 식별 안 됨)</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>국립대구과학관</t>
+          <t>한국의약품안전관리원</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
@@ -22758,33 +22758,33 @@
         </is>
       </c>
       <c r="D30" s="3" t="n">
-        <v>147</v>
+        <v>103.4</v>
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t>중(실 단위 조직명은 보도·인사자료로 확인, 전산 전담부서명·소속은 미확정)</t>
+          <t>중(공식 홈페이지 조직도는 JS 렌더링으로 트리 미확정 / 기관 공식 채널·보도자료·공공기록으로 정보화팀·의통팀·약물역학빅데이터팀 등 확인)</t>
         </is>
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t>IT최상위 확인불가 / AI전담 확인불가</t>
+          <t>AI전담 확인불가</t>
         </is>
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>확인불가 (별도 IT 본부·처·실 없음 — 실 단위 조직 중 '경영관리실'이 전산·정보화 행정을 겸장하는 것으로 추정)</t>
+          <t>정보화팀 (기획경영본부 산하)</t>
         </is>
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t>확인불가 (전담조직 미확인)</t>
+          <t>확인불가 (별도 'AI' 명칭 전담조직은 현 조직도에서 미확인 — 약물역학빅데이터팀이 빅데이터·AI 기능 일부 수행 추정)</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>한국로봇산업진흥원</t>
+          <t>한국형사·법무정책연구원</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
@@ -22798,224 +22798,24 @@
         </is>
       </c>
       <c r="D31" s="3" t="n">
-        <v>117</v>
+        <v>101</v>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>중(공식 홈페이지 도메인 확정 + 2026.5 개편 보도 교차, 내부 정보화 조직 직제는 미확인)</t>
+          <t>중(위키 1출처, 공식 조직도 직접 미확인)</t>
         </is>
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t>IT최상위 확인불가</t>
+          <t>AI전담 확인불가</t>
         </is>
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>확인불가 (별도 정보화 본부·실 없음 — 2본부 2실 체제, 정보화는 경영기획실 산하 기능으로 추정)</t>
+          <t>지식정보팀 (경영지원실 산하)</t>
         </is>
       </c>
       <c r="H31" s="3" t="inlineStr">
-        <is>
-          <t>있음(AX 본부 형태 — 단, AI 기술전담이 아닌 로봇산업진흥 본부)</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="3" t="inlineStr">
-        <is>
-          <t>한국여성정책연구원</t>
-        </is>
-      </c>
-      <c r="B32" s="3" t="inlineStr">
-        <is>
-          <t>기타</t>
-        </is>
-      </c>
-      <c r="C32" s="3" t="inlineStr">
-        <is>
-          <t>기타공공기관</t>
-        </is>
-      </c>
-      <c r="D32" s="3" t="n">
-        <v>116</v>
-      </c>
-      <c r="E32" s="3" t="inlineStr">
-        <is>
-          <t>중(공식 1출처 + 위키 보조 / IT·AI 세부조직 확인불가)</t>
-        </is>
-      </c>
-      <c r="F32" s="3" t="inlineStr">
-        <is>
-          <t>IT최상위 확인불가</t>
-        </is>
-      </c>
-      <c r="G32" s="3" t="inlineStr">
-        <is>
-          <t>확인불가 (경영지원본부 산하 추정)</t>
-        </is>
-      </c>
-      <c r="H32" s="3" t="inlineStr">
-        <is>
-          <t>없음 (확인불가에 가까움 — 별도 AI조직 단서 없음)</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="3" t="inlineStr">
-        <is>
-          <t>국립인천해양박물관</t>
-        </is>
-      </c>
-      <c r="B33" s="3" t="inlineStr">
-        <is>
-          <t>기타</t>
-        </is>
-      </c>
-      <c r="C33" s="3" t="inlineStr">
-        <is>
-          <t>기타공공기관</t>
-        </is>
-      </c>
-      <c r="D33" s="3" t="n">
-        <v>105</v>
-      </c>
-      <c r="E33" s="3" t="inlineStr">
-        <is>
-          <t>중(공식 홈페이지 메뉴구조 확인, 상세 조직도는 JS 렌더링으로 부서 세부 미확정)</t>
-        </is>
-      </c>
-      <c r="F33" s="3" t="inlineStr">
-        <is>
-          <t>IT최상위 확인불가</t>
-        </is>
-      </c>
-      <c r="G33" s="3" t="inlineStr">
-        <is>
-          <t>확인불가 (정보화·전산 전담조직 식별 안 됨 — 신설 소규모 박물관, 경영지원실 내 총무 기능에 포함 추정)</t>
-        </is>
-      </c>
-      <c r="H33" s="3" t="inlineStr">
-        <is>
-          <t>없음</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="3" t="inlineStr">
-        <is>
-          <t>한국저작권보호원</t>
-        </is>
-      </c>
-      <c r="B34" s="3" t="inlineStr">
-        <is>
-          <t>기타</t>
-        </is>
-      </c>
-      <c r="C34" s="3" t="inlineStr">
-        <is>
-          <t>기타공공기관</t>
-        </is>
-      </c>
-      <c r="D34" s="3" t="n">
-        <v>104.8</v>
-      </c>
-      <c r="E34" s="3" t="inlineStr">
-        <is>
-          <t>상(공식 홈페이지 조직도 + 공공데이터포털 관리부서 표기 교차확인)</t>
-        </is>
-      </c>
-      <c r="F34" s="3" t="inlineStr">
-        <is>
-          <t>AI전담 확인불가</t>
-        </is>
-      </c>
-      <c r="G34" s="3" t="inlineStr">
-        <is>
-          <t>정보기술부</t>
-        </is>
-      </c>
-      <c r="H34" s="3" t="inlineStr">
-        <is>
-          <t>확인불가 (별도 AI 전담조직 식별 안 됨)</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="3" t="inlineStr">
-        <is>
-          <t>한국의약품안전관리원</t>
-        </is>
-      </c>
-      <c r="B35" s="3" t="inlineStr">
-        <is>
-          <t>기타</t>
-        </is>
-      </c>
-      <c r="C35" s="3" t="inlineStr">
-        <is>
-          <t>기타공공기관</t>
-        </is>
-      </c>
-      <c r="D35" s="3" t="n">
-        <v>103.4</v>
-      </c>
-      <c r="E35" s="3" t="inlineStr">
-        <is>
-          <t>중(공식 홈페이지 조직도는 JS 렌더링으로 트리 미확정 / 기관 공식 채널·보도자료·공공기록으로 정보화팀·의통팀·약물역학빅데이터팀 등 확인)</t>
-        </is>
-      </c>
-      <c r="F35" s="3" t="inlineStr">
-        <is>
-          <t>AI전담 확인불가</t>
-        </is>
-      </c>
-      <c r="G35" s="3" t="inlineStr">
-        <is>
-          <t>정보화팀 (기획경영본부 산하)</t>
-        </is>
-      </c>
-      <c r="H35" s="3" t="inlineStr">
-        <is>
-          <t>확인불가 (별도 'AI' 명칭 전담조직은 현 조직도에서 미확인 — 약물역학빅데이터팀이 빅데이터·AI 기능 일부 수행 추정)</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="3" t="inlineStr">
-        <is>
-          <t>한국형사·법무정책연구원</t>
-        </is>
-      </c>
-      <c r="B36" s="3" t="inlineStr">
-        <is>
-          <t>기타</t>
-        </is>
-      </c>
-      <c r="C36" s="3" t="inlineStr">
-        <is>
-          <t>기타공공기관</t>
-        </is>
-      </c>
-      <c r="D36" s="3" t="n">
-        <v>101</v>
-      </c>
-      <c r="E36" s="3" t="inlineStr">
-        <is>
-          <t>중(위키 1출처, 공식 조직도 직접 미확인)</t>
-        </is>
-      </c>
-      <c r="F36" s="3" t="inlineStr">
-        <is>
-          <t>AI전담 확인불가</t>
-        </is>
-      </c>
-      <c r="G36" s="3" t="inlineStr">
-        <is>
-          <t>지식정보팀 (경영지원실 산하)</t>
-        </is>
-      </c>
-      <c r="H36" s="3" t="inlineStr">
         <is>
           <t>확인불가 (전담 AI조직 미확인)</t>
         </is>

--- a/IT조직_비교표_공공기관274.xlsx
+++ b/IT조직_비교표_공공기관274.xlsx
@@ -16795,17 +16795,17 @@
       </c>
       <c r="F218" s="3" t="inlineStr">
         <is>
-          <t>경영관리본부 (인사노무처 내 정보보안·개인정보 담당)</t>
+          <t>경영관리본부 (산하 인사노무처 내 정보보안·개인정보 담당)</t>
         </is>
       </c>
       <c r="G218" s="3" t="inlineStr">
         <is>
-          <t>팀 (본부 산하) — 별도 IT 전담 부서 없음</t>
+          <t>팀 (본부 산하) — 별도 IT 전담 부서 없음, 인사노무처 내 담당자 배치</t>
         </is>
       </c>
       <c r="H218" s="3" t="inlineStr">
         <is>
-          <t>확인불가 (인사노무처 내 정보보안·개인정보 담당자 배치, 별도 정보화팀 미확인)</t>
+          <t>인사노무처 (총무팀·인사팀과 함께 '정보보안·개인정보' 담당자 1인 배치; 별도 정보화/전산 전담 팀 미설치)</t>
         </is>
       </c>
       <c r="I218" s="3" t="inlineStr">
@@ -16825,22 +16825,22 @@
       </c>
       <c r="L218" s="3" t="inlineStr">
         <is>
-          <t>확인불가 (경영관리본부장 총괄 추정)</t>
+          <t>경영관리본부장 총괄 (인사노무처 소관, 별도 전담 CIO 직위 미확인)</t>
         </is>
       </c>
       <c r="M218" s="3" t="inlineStr">
         <is>
-          <t>인사노무처 내 정보보안·개인정보 담당 (전담 CISO 부서 미확인)</t>
+          <t>인사노무처 내 정보보안·개인정보 담당자(02-390-5989)가 실무 수행. 모회사 코레일과 정보보안·개인정보 보호 실무협의회 체계로 연계(코레일 디지털융합본부장이 계열사 개인정보보호 최고책임자(CPO) 역할로 총괄·지원). 자체 전담 임원급 CISO 부서는 미설치</t>
         </is>
       </c>
       <c r="N218" s="3" t="inlineStr">
         <is>
-          <t>중(공식 1출처)</t>
+          <t>상(공식 조직도·부서별 연락처 + 모회사 코레일 보안협의회 보도 교차확인)</t>
         </is>
       </c>
       <c r="O218" s="3" t="inlineStr">
         <is>
-          <t>대표이사 직속에 감사실·안전경영실, 경영관리본부(기획전략처·인사노무처), 영업본부(물류기획처·물류영업처), 부산·의왕·여수 지사 및 철도사업소(31개소 이상) 구조. 별도 정보화/IT 전담 조직이 없으며 정보보안·개인정보 기능이 인사노무처에 포함. AI 전담조직 없음.</t>
+          <t>한국철도공사(코레일) 출자 자회사(철도 물류·컨테이너·화물 전문). 조직: 대표이사 직속 감사실·안전경영실, 경영관리본부(경영기획처·인사노무처), 영업본부(물류계획처·물류영업처), 철도운영단(운영관리처), 부산·의왕·여수 지점. 별도 정보화/IT 전담 조직 없이 정보보안·개인정보 기능이 인사노무처에 포함. 코레일이 5개 계열사(코레일로지스 포함)와 '정보보안·개인정보 보호 실무협의회'·'정보보안 7대 실천 프로그램' 등 공동 보안체계 운영 → 모회사 IT/보안 거버넌스에 일부 편입. AI 전담조직 없음.</t>
         </is>
       </c>
     </row>
@@ -17020,52 +17020,52 @@
       </c>
       <c r="F221" s="3" t="inlineStr">
         <is>
-          <t>디지털전환팀(DAX팀) — 행정·경영지원 라인 소속 (추정)</t>
+          <t>경영지원실 (산하 디지털전환팀(DAX팀)이 지식정보·전산·디지털전환 담당)</t>
         </is>
       </c>
       <c r="G221" s="3" t="inlineStr">
         <is>
+          <t>팀 (실 산하) — 경영지원실 산하 디지털전환팀</t>
+        </is>
+      </c>
+      <c r="H221" s="3" t="inlineStr">
+        <is>
+          <t>디지털전환팀(DAX팀, 지식정보+총무 통합) — 경영지원실 소속</t>
+        </is>
+      </c>
+      <c r="I221" s="3" t="inlineStr">
+        <is>
+          <t>확인불가 (전담 AI 조직 미확인 — 디지털·AI 전환 대응은 디지털전환팀이 수행)</t>
+        </is>
+      </c>
+      <c r="J221" s="3" t="inlineStr">
+        <is>
+          <t>디지털전환팀(DAX팀) (전사 디지털·AI 전환 대응 기능 보유)</t>
+        </is>
+      </c>
+      <c r="K221" s="3" t="inlineStr">
+        <is>
           <t>팀</t>
         </is>
       </c>
-      <c r="H221" s="3" t="inlineStr">
-        <is>
-          <t>디지털전환팀(DAX팀, 지식정보+총무 통합), 시스템혁신실(연구조직)</t>
-        </is>
-      </c>
-      <c r="I221" s="3" t="inlineStr">
-        <is>
-          <t>확인불가 (전담 AI 조직 미확인 — 디지털·AI 전환 대응은 디지털전환팀이 수행)</t>
-        </is>
-      </c>
-      <c r="J221" s="3" t="inlineStr">
-        <is>
-          <t>디지털전환팀(DAX팀) (전사 디지털·AI 전환 대응 기능 보유)</t>
-        </is>
-      </c>
-      <c r="K221" s="3" t="inlineStr">
-        <is>
-          <t>팀</t>
-        </is>
-      </c>
       <c r="L221" s="3" t="inlineStr">
         <is>
-          <t>확인불가</t>
+          <t>확인불가 (전담 CIO 직위 미확인 — 디지털전환 소관 경영지원실장이 정보화 총괄 추정)</t>
         </is>
       </c>
       <c r="M221" s="3" t="inlineStr">
         <is>
-          <t>확인불가</t>
+          <t>개인정보보호책임자(CPO) = 경영지원실장(곽미선), 보호담당자 = 경영지원실 디지털전환팀(이은호). 정부출연연구기관으로 별도 임원급 CISO 신고의무 통상 면제대상이며 정보보호·개인정보 총괄은 경영지원실장이 수행</t>
         </is>
       </c>
       <c r="N221" s="3" t="inlineStr">
         <is>
-          <t>중(공식 홈페이지 조직도 이미지 + 2026 개편 보도 다수 교차확인, 단 정확한 소속 라인 이미지 미파싱)</t>
+          <t>상(공식 홈페이지 개인정보처리방침으로 경영지원실·디지털전환팀 소속·CPO 확인 + 2026 개편 보도 다수 교차확인)</t>
         </is>
       </c>
       <c r="O221" s="3" t="inlineStr">
         <is>
-          <t>2026년 조직개편(PBS 폐지 대응)으로 기존 인사총무팀 총무 기능과 지식정보 업무를 통합해 '디지털전환팀(DAX팀)'으로 재편. 디지털·AI 전환 대응력 강화 목적. 연구조직으로 '시스템혁신실' 보유(데이터 안전망 등 연구 수행).</t>
+          <t>2026.2.23 조직개편(인공지능 기반 디지털 전환 및 PBS 폐지 대응)으로 1본부·3센터·4실·7팀 → 1본부·3센터·4실·8팀 체제로 변경. 기존 인사총무팀 총무기능과 지식정보 업무를 통합해 '디지털전환팀(DAX팀)'으로 재편(경영지원실 소속), 기획조정팀을 성과확산팀과 분리. 연구본부는 시스템혁신본부·혁신성장본부·글로벌전략본부(2026 본부장 전보). 연구조직으로 '시스템혁신실/시스템혁신 연구분야' 별도 보유(데이터·디지털 정책 연구).</t>
         </is>
       </c>
     </row>
@@ -17170,52 +17170,52 @@
       </c>
       <c r="F223" s="3" t="inlineStr">
         <is>
-          <t>확인불가 (별도 IT 본부·처·실 없음 — 실 단위 조직 중 '경영관리실'이 전산·정보화 행정을 겸장하는 것으로 추정)</t>
+          <t>경영기획본부 (산하 경영지원실이 전산·정보화·정보보안 행정 겸장)</t>
         </is>
       </c>
       <c r="G223" s="3" t="inlineStr">
         <is>
-          <t>확인불가 (별도 IT 조직 단위 없음 — 경영관리실 내 담당 수준 추정)</t>
+          <t>처·실(본부 산하) — 경영기획본부 산하 경영지원실 (별도 IT 전담 조직 없음)</t>
         </is>
       </c>
       <c r="H223" s="3" t="inlineStr">
         <is>
-          <t>확인불가 (전산·정보화 전담 부서명 미확인 / 경영관리실 산하 담당 추정)</t>
+          <t>경영지원실 (총무·회계·인사와 함께 전산·정보화·정보보안 담당 / 전담 부서명 미확인)</t>
         </is>
       </c>
       <c r="I223" s="3" t="inlineStr">
         <is>
-          <t>확인불가 (전담조직 미확인)</t>
+          <t>없음 (전담 조직 미확인 — 사내 AI 전담조직 없음)</t>
         </is>
       </c>
       <c r="J223" s="3" t="inlineStr">
         <is>
-          <t>확인불가</t>
+          <t>해당없음</t>
         </is>
       </c>
       <c r="K223" s="3" t="inlineStr">
         <is>
-          <t>확인불가</t>
+          <t>해당없음</t>
         </is>
       </c>
       <c r="L223" s="3" t="inlineStr">
         <is>
-          <t>확인불가</t>
+          <t>확인불가 (전담 CIO 직위 미확인 — 경영기획본부장/경영지원실장이 정보화 총괄 추정)</t>
         </is>
       </c>
       <c r="M223" s="3" t="inlineStr">
         <is>
-          <t>확인불가</t>
+          <t>확인불가 (별도 임원급 CISO 부서 명시 미확인 — 통상 경영지원실장이 개인정보보호책임자(CPO)·정보보호 총괄 겸임 추정)</t>
         </is>
       </c>
       <c r="N223" s="3" t="inlineStr">
         <is>
-          <t>중(실 단위 조직명은 보도·인사자료로 확인, 전산 전담부서명·소속은 미확정)</t>
+          <t>중(본부·실 조직구성은 위키백과(2026.5 갱신)·조직개편 보도로 확인, 전산 전담부서명·CIO/CISO 직접확인은 미흡)</t>
         </is>
       </c>
       <c r="O223" s="3" t="inlineStr">
         <is>
-          <t>과학기술정보통신부 산하 전시·과학교육 중심 법인(관장=이사장 겸임, 현 관장 이난희). 실 단위 조직 구성: 전략기획실, 전시기획연구실, 과학문화실, 경영관리실, 교육연구실, 전시관운영센터, 시설관리센터(2022년 첫 조직개편 + 2025.12 운영체계 개편 반영). 전산·정보화 행정은 경영관리실(총무·회계·관리 총괄)이 겸장하는 것으로 추정되나 전담 부서명 미확인. 임직원 다수 AI활용지도사 취득·AI 전시콘텐츠 개발 등 AI를 전시·교육에 활용하나 사내 IT/AI 전담조직은 없음.</t>
+          <t>과기정통부 산하 전시·과학교육 중심 법인(관장=이사장 겸임, 현 관장 이난희). 조직(공식 현행): 관장 직속 대외협력실 + 경영기획본부(기획예산실·경영지원실·시설안전센터) + 전시교육본부(전시기획실·과학문화실·과학교육실·전시운영센터)의 2본부 체계. 2022.1 첫 조직개편(전시기획실→전시기획연구실, 전시관운영센터·시설관리센터 신설) 후 2025.12 이사회 의결로 본부 체계로 재편(전문성·자체 연구기능 강화). 전산·정보화 행정은 경영지원실(총무·회계·인사 총괄)이 겸장. 임직원 44명 AI활용지도사 1급 취득 등 'AI 활용 스마트 과학관' 추진(전시·교육·행정 AI 적용)하나 사내 IT/AI 전담조직은 없음.</t>
         </is>
       </c>
     </row>
@@ -17470,17 +17470,17 @@
       </c>
       <c r="F227" s="3" t="inlineStr">
         <is>
-          <t>경영지원실 (정보화·전산 업무 소관으로 추정)</t>
+          <t>경영지원실 (정보화·전산·정보보안 업무 소관)</t>
         </is>
       </c>
       <c r="G227" s="3" t="inlineStr">
         <is>
-          <t>실(IT 전담 별도 조직 없음, 경영지원실 산하 업무로 추정)</t>
+          <t>실(IT 전담 별도 조직 없음, 경영지원실 산하 업무)</t>
         </is>
       </c>
       <c r="H227" s="3" t="inlineStr">
         <is>
-          <t>확인불가 (별도 정보화 전담 팀 명칭 미확인)</t>
+          <t>경영지원실 내 전산·정보화 담당 (별도 정보화 전담 팀 명칭 미확인 / 전산장비·정보보안장비 유지보수 경영지원실 소관 확인)</t>
         </is>
       </c>
       <c r="I227" s="3" t="inlineStr">
@@ -17500,22 +17500,22 @@
       </c>
       <c r="L227" s="3" t="inlineStr">
         <is>
-          <t>확인불가</t>
+          <t>확인불가 (전담 CIO 직위 미확인 — 경영지원실장이 정보화 총괄 추정)</t>
         </is>
       </c>
       <c r="M227" s="3" t="inlineStr">
         <is>
-          <t>확인불가</t>
+          <t>경영지원실 소관(정보보안장비 유지보수·전산 업무 경영지원실 처리 확인). 별도 임원급 CISO 부서 명시는 미확인 — 통상 경영지원실장이 개인정보보호책임자(CPO)·정보보호 총괄 겸임 추정</t>
         </is>
       </c>
       <c r="N227" s="3" t="inlineStr">
         <is>
-          <t>중(공식 내규집 부서목록 1출처, IT 소관부서 직접확인은 미흡)</t>
+          <t>중(공식 내규집 부서목록 + 채용공고·기록물대장으로 경영지원실 IT소관 정황 확인, IT 전담 팀명·CISO 직접확인은 미흡)</t>
         </is>
       </c>
       <c r="O227" s="3" t="inlineStr">
         <is>
-          <t>동남권 지역거점 과학관(2015년 개관, 2017년 기타공공기관 지정). 조직은 경영지원실·기획예산실·전시연구실·전시운영센터·과학문화실·교육연구실·홍보협력실·시설안전센터·청렴감사팀 등으로 구성(2026.2 내규집 기준). 정보화/전산 전담 부서가 별도로 명시되지 않아 경영지원실 또는 기획예산실 내 업무로 추정.</t>
+          <t>동남권 지역거점 과학관(2015년 개관, 2017년 기타공공기관 지정). 조직: 경영지원실·기획예산실·전시연구실·전시운영센터·과학문화실·교육연구실·홍보협력실·시설안전센터·청렴감사팀 등(2026.2 내규집 기준). 경영지원실이 채용·인사·재무·총무 등 경영 전반 총괄(채용 문의 051-750-2461/2463)이며 전산·정보화·정보보안장비 유지보수도 경영지원실 소관으로 운영. 별도 정보화/전산 전담 팀은 미설치.</t>
         </is>
       </c>
     </row>
@@ -18820,17 +18820,17 @@
       </c>
       <c r="F245" s="3" t="inlineStr">
         <is>
-          <t>운영지원팀 (정보화·전산 업무 포함 추정)</t>
+          <t>경영혁신본부 (산하 사이버대응팀이 정보보안·개인정보·전산 담당)</t>
         </is>
       </c>
       <c r="G245" s="3" t="inlineStr">
         <is>
-          <t>팀 (사무총장 직속 팀)</t>
+          <t>팀 (본부 산하) — 경영혁신본부 산하 사이버대응팀</t>
         </is>
       </c>
       <c r="H245" s="3" t="inlineStr">
         <is>
-          <t>확인불가 (별도 IT 전담부서 미확인)</t>
+          <t>사이버대응팀 (정보보안, 개인정보보호, 공공데이터 제공 및 데이터 기반 행정 담당; 차장 1 + 주임 1)</t>
         </is>
       </c>
       <c r="I245" s="3" t="inlineStr">
@@ -18840,32 +18840,32 @@
       </c>
       <c r="J245" s="3" t="inlineStr">
         <is>
-          <t>확인불가</t>
+          <t>해당없음</t>
         </is>
       </c>
       <c r="K245" s="3" t="inlineStr">
         <is>
-          <t>확인불가</t>
+          <t>해당없음</t>
         </is>
       </c>
       <c r="L245" s="3" t="inlineStr">
         <is>
-          <t>확인불가 (사무총장/운영지원팀장 총괄 추정)</t>
+          <t>확인불가 (전담 CIO 직위 미확인 — 경영혁신본부장(부장) 총괄 추정)</t>
         </is>
       </c>
       <c r="M245" s="3" t="inlineStr">
         <is>
-          <t>확인불가</t>
+          <t>사이버대응팀(차장)이 정보보안·개인정보보호 실무 총괄, 경영혁신본부 소속. 별도 임원급 CISO 직위 명시는 미확인(소규모 기관)</t>
         </is>
       </c>
       <c r="N245" s="3" t="inlineStr">
         <is>
-          <t>중(위키 조직정보 + 검색 교차, 공식 조직도 페이지 직접 접속 실패)</t>
+          <t>상(공식 조직도 부서별 명단 + Public Policy Wiki 조직도·연락처 교차확인)</t>
         </is>
       </c>
       <c r="O245" s="3" t="inlineStr">
         <is>
-          <t>사무총장 산하 운영지원팀·예방사업팀·중독재활팀의 소규모 사업 중심 조직. 별도 정보화 본부/처/팀 없음. 2024년 식약처 산하 공공기관으로 지정된 신규 공공기관으로, 조직 정비 진행 중일 가능성. IT/정보화는 운영지원팀 내에서 수행되는 것으로 추정.</t>
+          <t>2024년 식약처 산하 공공기관 지정 후 조직 정비 완료. 현 조직(공식 조직도 기준): 이사장 → 감사팀·상임이사(사무총장) → 경영혁신본부(경영기획팀·경영관리팀·사이버대응팀)·예방재활본부(예방사업팀·중독재활팀·1342용기한걸음센터) + 14지부 17센터. 총 2본부 6팀 1센터 및 14지부 17센터, 부설기관 마약퇴치전문교육원. 정보보안·개인정보·전산·공공데이터가 '사이버대응팀'으로 별도 분리 신설된 점이 소규모 기관 치고 특징적(공공기관 전환에 따른 보안·데이터 거버넌스 강화). AI 전담조직은 미확인.</t>
         </is>
       </c>
     </row>
@@ -19045,52 +19045,52 @@
       </c>
       <c r="F248" s="3" t="inlineStr">
         <is>
-          <t>경영기획본부 (정보화·전산 업무 소관)</t>
+          <t>경영기획본부 (정보화 소관) — 산하 '지식정보팀'이 정보화·전산 담당</t>
         </is>
       </c>
       <c r="G248" s="3" t="inlineStr">
         <is>
-          <t>처·실(본부 산하) — 본부 내 팀 단위(팀명 확인불가)</t>
+          <t>팀 — 경영기획본부 산하 '지식정보팀'(본부 내 팀 단위)</t>
         </is>
       </c>
       <c r="H248" s="3" t="inlineStr">
         <is>
-          <t>확인불가 (경영기획본부 내 정보화/전산 담당 팀, 별도 명칭 미확인)</t>
+          <t>지식정보팀 (경영기획본부 산하. IT·정보화·전산 담당. 경영기획본부는 경영지원팀·운영지원팀·지식정보팀으로 구성)</t>
         </is>
       </c>
       <c r="I248" s="3" t="inlineStr">
         <is>
-          <t>없음</t>
+          <t>없음 (별도 AI 전담조직 직제 없음 — 단, 사업조직인 중앙디지털성범죄피해자지원센터가 AI 기반 성착취물 자동탐지·삭제 기술을 운용)</t>
         </is>
       </c>
       <c r="J248" s="3" t="inlineStr">
         <is>
-          <t>확인불가</t>
+          <t>해당없음 (전담조직 부재)</t>
         </is>
       </c>
       <c r="K248" s="3" t="inlineStr">
         <is>
-          <t>확인불가</t>
+          <t>해당없음</t>
         </is>
       </c>
       <c r="L248" s="3" t="inlineStr">
         <is>
-          <t>확인불가 (경영기획본부장 총괄 추정)</t>
+          <t>경영기획본부장 총괄 (정보화 소관 본부 = 경영기획본부, 지식정보팀이 실무) — 전담 CIO 명문 미확인</t>
         </is>
       </c>
       <c r="M248" s="3" t="inlineStr">
         <is>
-          <t>확인불가</t>
+          <t>확인불가 (경영기획본부장/지식정보팀 라인 추정 — 유사 공공기관 다수가 경영기획본부장을 CPO로 지정. 본 기관 전용 처리방침 직접 확인 실패)</t>
         </is>
       </c>
       <c r="N248" s="3" t="inlineStr">
         <is>
-          <t>중(공식 위키 본부 구성 + 채용/검색 교차, 경영기획본부 내 IT 팀명·공식 조직도 페이지 직접 확인 실패)</t>
+          <t>상(채용공고 2출처[링커리어·사람인]로 경영기획본부 산하 지식정보팀의 IT/AI 직무 교차 확인 + 연합뉴스로 AI 탐지시스템 운용 확인. 공식 조직도 페이지는 JS렌더링·404로 직접 트리 미확인이나 정보화 담당팀명 확정)</t>
         </is>
       </c>
       <c r="O248" s="3" t="inlineStr">
         <is>
-          <t>경영기획본부·교육개발본부·여성폭력방지본부·인권보호본부 + 일본군'위안부'문제연구소 구성. 인권보호본부 산하 "디지털성범죄피해자지원센터"가 디지털성범죄 대응(불법촬영물 삭제지원 등) 사업을 수행하며 IT기술을 활용하나, 이는 피해자지원 사업조직이지 내부 IT/정보화 전담조직이 아님에 유의. 내부 정보화는 경영기획본부 소관.</t>
+          <t>경영기획본부·여성폭력방지본부·인권보호본부(중앙디지털성범죄피해자지원센터·여성긴급전화1366중앙센터 포함)·일본군'위안부'문제연구소 등으로 구성. 경영기획본부 산하 '지식정보팀'이 내부 정보화·전산을 담당(2026년 채용에서 지식정보팀이 네트워크·정보통신·AI(인공지능) 직무 모집). 한편 인권보호본부 산하 '중앙디지털성범죄피해자지원센터'는 AI 기반 성착취물 자동탐지·삭제 시스템(채팅앱 최초 적용, 2018년부터 축적 데이터 학습)을 운용하나 이는 피해자지원 사업조직이지 내부 IT/AI 전담조직이 아님. 중앙디성센터 산하 '삭제기술팀'도 별도 존재.</t>
         </is>
       </c>
     </row>
@@ -19570,17 +19570,17 @@
       </c>
       <c r="F255" s="3" t="inlineStr">
         <is>
-          <t>AI디지털전환부</t>
+          <t>AI디지털전환부 (경영본부 산하) — 직전 명칭 '전산정보부'</t>
         </is>
       </c>
       <c r="G255" s="3" t="inlineStr">
         <is>
-          <t>부(본부 산하) — 본부 소속 확인불가(2본부 8부 1소 1실 체계)</t>
+          <t>처·실(본부 산하) — 경영본부 소속 '부' 단위 (2본부 8부 1소 1실 체계)</t>
         </is>
       </c>
       <c r="H255" s="3" t="inlineStr">
         <is>
-          <t>확인불가 (AI디지털전환부 산하 팀/파트 세부 미확인). 별도 통합전산센터(전산운영 시설) 운영</t>
+          <t>확인불가 (AI디지털전환부/전산정보부 산하 팀·파트 세부 미확인). 별도 통합전산센터(전산운영 시설, 세종 신사옥 내) 운영</t>
         </is>
       </c>
       <c r="I255" s="3" t="inlineStr">
@@ -19590,32 +19590,32 @@
       </c>
       <c r="J255" s="3" t="inlineStr">
         <is>
-          <t>AI디지털전환부 (정보화·디지털전환·AI·데이터 업무를 포괄하는 부서명)</t>
+          <t>AI디지털전환부 (정보화·디지털전환·AI·데이터 업무를 포괄하는 부서명. 구 '전산정보부'에서 명칭 변경)</t>
         </is>
       </c>
       <c r="K255" s="3" t="inlineStr">
         <is>
-          <t>부(본부 산하 추정)</t>
+          <t>부(경영본부 산하)</t>
         </is>
       </c>
       <c r="L255" s="3" t="inlineStr">
         <is>
-          <t>확인불가 (AI디지털전환부장이 정보화 총괄 추정, 전담 CIO 명문 표기 미확인)</t>
+          <t>경영본부장(전무이사) 총괄 추정 — 정보화·개인정보보호 업무 소관 본부가 경영본부로 확인</t>
         </is>
       </c>
       <c r="M255" s="3" t="inlineStr">
         <is>
-          <t>확인불가</t>
+          <t>확인불가 (별도 CISO 명문 미확인). 개인정보 보호책임관(CPO)은 경영본부 전무이사, 개인정보 보호담당자는 전산정보부(현 AI디지털전환부) 차장 — 정보보호·개인정보 업무가 IT부서·경영본부 라인에 편제</t>
         </is>
       </c>
       <c r="N255" s="3" t="inlineStr">
         <is>
-          <t>중(공공데이터포털 제공부서 표기 + 부서현황 데이터셋 교차, 공식 홈페이지 조직도 트리는 직접 미확인)</t>
+          <t>상(공식 개인정보처리방침 PDF + 공공데이터포털 제공부서 + 부서현황 데이터셋 + 주요업무보고 교차 / AI디지털전환부의 정확한 산하 팀 트리만 미확인)</t>
         </is>
       </c>
       <c r="O255" s="3" t="inlineStr">
         <is>
-          <t>전국 16~17개 지역신용보증재단과 공동 구축한 통합정보시스템을 운영(통합전산센터를 세종 신사옥 내 구축). 정보화 부서 명칭을 'AI디지털전환부'로 두어 AI·디지털전환을 전담 부서명에 명시 — IT/AI 통합형 조직. 모바일 비대면 보증채널·공공마이데이터·AI 리스크관리 시스템 등 디지털 사업 추진 중. 2025년 AI·데이터 활용 아이디어 경진대회 개최.</t>
+          <t>전국 16~17개 지역신용보증재단과 공동 구축한 통합정보시스템을 운영(통합전산센터를 세종 신사옥 내 구축). 정보화 부서 명칭을 '전산정보부'에서 'AI디지털전환부'로 변경하여 AI·디지털전환을 전담 부서명에 명시 — IT/AI 통합형 조직. '26~'28 중장기정보화전략계획(2025.7 수립) 6대 과제에 ④지능형 고객상담시스템(AICC) ⑤생성형AI 기반 BI 시스템 고도화 ⑥재단 업무지원 AI 어시스턴트 구축 등 AI 사업 다수 포함. 모바일 비대면 보증채널·공공마이데이터 도입. 2025년 AI·데이터 활용 아이디어 경진대회 개최(LLM 기반 상담·민원 자동응대 등 수상). 회장 원영준, 본사 세종(서울사무소 마포).</t>
         </is>
       </c>
     </row>
@@ -19795,27 +19795,27 @@
       </c>
       <c r="F258" s="3" t="inlineStr">
         <is>
-          <t>확인불가 (별도 정보화 본부·실 없음 — 2본부 2실 체제, 정보화는 경영기획실 산하 기능으로 추정)</t>
+          <t>경영지원실 (정보화·전산·정보보안 소관) — 산하 '안전보안팀'이 정보보안·개인정보보호 담당</t>
         </is>
       </c>
       <c r="G258" s="3" t="inlineStr">
         <is>
-          <t>확인불가 (팀 레벨 추정)</t>
+          <t>팀 — 경영지원실 산하 '안전보안팀'(실 내 팀 단위). 별도 정보화 본부·처 없음</t>
         </is>
       </c>
       <c r="H258" s="3" t="inlineStr">
         <is>
-          <t>확인불가 (정보화/전산 담당 팀 명칭 미확인). 경영기획실 산하 기획예산팀·인재경영팀 등 확인되나 정보화 전담팀 명칭은 미확인</t>
+          <t>안전보안팀 (정보보안·개인정보보호·안전 담당. 경영지원실 산하). 일반 정보화·전산 운영도 경영지원실 소관</t>
         </is>
       </c>
       <c r="I258" s="3" t="inlineStr">
         <is>
-          <t>있음(AX 본부 형태 — 단, AI 기술전담이 아닌 로봇산업진흥 본부)</t>
+          <t>있음(AX 본부 형태 — 단, 기관 내부 IT 전담이 아닌 로봇산업진흥 사업본부)</t>
         </is>
       </c>
       <c r="J258" s="3" t="inlineStr">
         <is>
-          <t>산업AX혁신본부 / 기술기반AX본부 (2026.5 개편, 각각 구 제조로봇본부·서비스로봇본부에서 명칭 변경. 'AX'는 AI·디지털전환 의미)</t>
+          <t>산업AX혁신본부 / 기술기반AX본부 (2026.5.1 개편, 각각 구 제조로봇본부·서비스로봇본부에서 명칭 변경. 'AX'=AI 전환)</t>
         </is>
       </c>
       <c r="K258" s="3" t="inlineStr">
@@ -19825,22 +19825,22 @@
       </c>
       <c r="L258" s="3" t="inlineStr">
         <is>
-          <t>확인불가</t>
+          <t>경영지원실장 총괄 추정 (정보화·전산 소관 = 경영지원실, 전담 CIO 명문 미확인)</t>
         </is>
       </c>
       <c r="M258" s="3" t="inlineStr">
         <is>
-          <t>확인불가</t>
+          <t>안전보안팀장 (정보보안·개인정보 분야별 책임자). 개인정보보호책임자(CPO)는 경영지원실장(현 정준혁) / 직전 3본부 체제에서는 경영기획본부장(류지호) — 정보보안 라인이 경영지원실-안전보안팀으로 편제</t>
         </is>
       </c>
       <c r="N258" s="3" t="inlineStr">
         <is>
-          <t>중(공식 홈페이지 도메인 확정 + 2026.5 개편 보도 교차, 내부 정보화 조직 직제는 미확인)</t>
+          <t>상(공식 개인정보처리방침 2판[3본부 체제·2본부2실 체제]으로 정보보안 담당조직 확정 + 2026.5 개편 보도 다수 교차)</t>
         </is>
       </c>
       <c r="O258" s="3" t="inlineStr">
         <is>
-          <t>2026.5.1자 조직개편으로 '2본부 2실' 체제. 제조로봇본부→산업AX혁신본부, 서비스로봇본부→기술기반AX본부로 명칭 변경(AI·로봇·휴머노이드 중심 산업전환 대응). 휴머노이드로봇센터·국가로봇테스트필드구축센터 신설, 대외협력TF팀 신설. 원장 조영훈. 대구 소재. 단, 이들 본부는 로봇산업 진흥 사업조직이며 기관 내부 '정보화(IT 운영)' 전담조직과는 성격이 다름. 직전(2022.1) 개편 시에는 '3본부 1실'(경영기획본부·로봇혁신사업본부·로봇기반디지털본부·산업혁신실) 체제였음 → 2026.5 재개편으로 현행 2본부 2실.</t>
+          <t>2026.5.1자 조직개편으로 '2본부 2실' 체제 유지. 제조로봇본부→산업AX혁신본부, 서비스로봇본부→기술기반AX본부로 명칭 변경(AI·로봇·휴머노이드 'AX(AI전환) G1' 대응). 휴머노이드로봇센터·국가로봇테스트필드구축센터·대외협력TF팀 신설. 원장 조영훈, 대구 소재. 단, 이들 본부는 로봇산업 진흥 사업조직이며 기관 내부 정보화(IT 운영)·정보보안 전담조직과는 성격이 다름 — 내부 IT/보안은 경영지원실(안전보안팀) 소관. 직전(2022.12/2023.1) 개편 시 '3본부 1실'(경영기획본부[기획예산팀·인재경영팀·재무회계팀·안전보안팀]·로봇혁신사업본부·로봇기반디지털본부·산업혁신실) 체제였음 → 2026.5 재개편으로 현행 2본부 2실.</t>
         </is>
       </c>
     </row>
@@ -20020,22 +20020,22 @@
       </c>
       <c r="F261" s="3" t="inlineStr">
         <is>
-          <t>확인불가 (경영지원본부 산하 추정)</t>
+          <t>정보지식공유센터 (성주류화지식혁신본부 산하) — 정보화·정보지식 공유·홈페이지/시스템 운영 담당</t>
         </is>
       </c>
       <c r="G261" s="3" t="inlineStr">
         <is>
-          <t>확인불가 (본부 내 팀 단위 추정)</t>
+          <t>처·실(본부 산하) — 본부 산하 '센터'(팀) 단위. 별도 정보화 본부·처 없음</t>
         </is>
       </c>
       <c r="H261" s="3" t="inlineStr">
         <is>
-          <t>확인불가</t>
+          <t>정보지식공유센터 (성주류화지식혁신본부 소속). 개인정보보호 실무는 경영지원본부 인사조직관리센터가 별도 담당</t>
         </is>
       </c>
       <c r="I261" s="3" t="inlineStr">
         <is>
-          <t>없음 (확인불가에 가까움 — 별도 AI조직 단서 없음)</t>
+          <t>없음 (별도 AI 전담조직 직제 없음 — AI는 연구주제로만 다룸: '인공지능 젠더편향 대응' 등 정책연구)</t>
         </is>
       </c>
       <c r="J261" s="3" t="inlineStr">
@@ -20050,22 +20050,22 @@
       </c>
       <c r="L261" s="3" t="inlineStr">
         <is>
-          <t>확인불가 (경영지원본부장 겸임 추정)</t>
+          <t>확인불가 (정보지식공유센터 소관 본부는 성주류화지식혁신본부, 정보화 총괄 전담 CIO 명문 미확인)</t>
         </is>
       </c>
       <c r="M261" s="3" t="inlineStr">
         <is>
-          <t>확인불가</t>
+          <t>경영지원본부장(CPO) — 개인정보보호책임자: 경영지원본부장(이현화), 개인정보보호담당자: 인사조직관리센터. 정보보안·개인정보 거버넌스가 경영지원본부 라인. 별도 CISO 명문은 미확인</t>
         </is>
       </c>
       <c r="N261" s="3" t="inlineStr">
         <is>
-          <t>중(공식 1출처 + 위키 보조 / IT·AI 세부조직 확인불가)</t>
+          <t>상(공식 개인정보처리방침[CPO·담당부서] + 위키백과 6본부 조직 + 공식 페이지 담당부서(정보지식공유센터) 교차 확인)</t>
         </is>
       </c>
       <c r="O261" s="3" t="inlineStr">
         <is>
-          <t>6개 본부(기획조정본부·여성미래연구본부·일과생애연구본부·젠더폭력연구본부·성주류화지식혁신본부·경영지원본부) 체제의 연구기관. IT·정보화 전담 본부·처·실 명칭이 공식 조직도에서 확인되지 않으며, 연구기관 특성상 정보화 기능은 경영지원본부 내 행정팀 단위에 배치된 것으로 추정. 위키백과 기준 부원장 아래 6본부 구성.</t>
+          <t>6개 본부(기획조정본부·여성미래연구본부·일과생애연구본부·젠더폭력연구본부·성주류화지식혁신본부·경영지원본부) 체제의 정부출연 연구기관. 정보화·정보지식 공유 기능은 '성주류화지식혁신본부' 산하 '정보지식공유센터'가 담당(성평등전략사업센터·성별영향평가센터·성인지예산센터·성인지데이터센터와 병렬). 개인정보보호 실무는 경영지원본부(인사조직관리센터)가 담당하여 정보화-개인정보 기능이 본부가 분리됨. 국내 최초 성인지 통계정보 시스템(2006~) 운영, 성인지데이터센터 보유. 임직원 약 132명(2025 4Q, 나무위키) 규모. 원장 김종숙. 서울 은평 소재.</t>
         </is>
       </c>
     </row>
@@ -20170,22 +20170,22 @@
       </c>
       <c r="F263" s="3" t="inlineStr">
         <is>
-          <t>ICT추진단</t>
+          <t>디지털홍보처 (사업관리본부 산하) — 정보화·디지털·개인정보보호 소관. 구 'ICT추진단'이 개편된 것으로 판단</t>
         </is>
       </c>
       <c r="G263" s="3" t="inlineStr">
         <is>
-          <t>단(団) — 본부 산하 또는 사장 직속 단위 (정확한 소속 본부 확인불가)</t>
+          <t>처·실(본부 산하) — 사업관리본부 산하 '처' 단위</t>
         </is>
       </c>
       <c r="H263" s="3" t="inlineStr">
         <is>
-          <t>확인불가</t>
+          <t>확인불가 (디지털홍보처 산하 팀 세부 미확인 — 홍보팀 등 포함 추정). 직제상 정보화·디지털·홍보·개인정보보호를 묶은 처</t>
         </is>
       </c>
       <c r="I263" s="3" t="inlineStr">
         <is>
-          <t>없음 (확인불가)</t>
+          <t>없음 (별도 AI 전담조직 직제 없음 — 단, AI 기반 개인정보 유·노출 탐지시스템 등 AI 기술 활용 진행)</t>
         </is>
       </c>
       <c r="J263" s="3" t="inlineStr">
@@ -20200,22 +20200,22 @@
       </c>
       <c r="L263" s="3" t="inlineStr">
         <is>
-          <t>확인불가</t>
+          <t>디지털홍보처장 총괄 추정 (정보화·디지털 소관 처 = 디지털홍보처). 소속 본부는 사업관리본부</t>
         </is>
       </c>
       <c r="M263" s="3" t="inlineStr">
         <is>
-          <t>확인불가 (개인정보 관리 우수기관 3년 연속, AI 기반 개인정보 유노출 탐지시스템 도입)</t>
+          <t>디지털홍보처장 (CPO 겸) — 개인정보 보호책임자: 디지털홍보처 박대훈 처장, 개인정보 보호담당자: 디지털홍보처 박현우 대리(privacy@sdco.or.kr). 별도 CISO 명문 미확인이나 정보보호·개인정보 라인이 디지털홍보처에 통합</t>
         </is>
       </c>
       <c r="N263" s="3" t="inlineStr">
         <is>
-          <t>중(공식 사업실명제·정보목록에서 ICT추진단 IT조직 확인 / 조직도 본부 소속관계는 JS렌더링으로 미확인)</t>
+          <t>상(공식 조직도 페이지[4본부 트리] + 공식 개인정보처리방침[CPO=디지털홍보처장] 2출처 교차 확인)</t>
         </is>
       </c>
       <c r="O263" s="3" t="inlineStr">
         <is>
-          <t>사장 직속 안전혁신실·감사실, 기획본부(기획조정실 등) 체제. 정보화·정보시스템 업무는 'ICT추진단'이 담당(차세대 통합행정업무·건설정보관리시스템 구축 등 정보화사업 수행 확인). AI 전담조직은 없으나 AI 기반 개인정보 탐지시스템 등 AI 기술 활용은 진행. 2019년 부→처 격상 및 대외협력처 신설 등 조직개편 이력.</t>
+          <t>사장 직속 안전혁신실·감사실, 그 아래 기획본부(기획조정실·인재경영처·재무관리처)·사업관리본부(사업관리처·디지털홍보처)·개발본부(사업계획처·관광산단처·개발사업처)·미래사업본부(에너지사업처·투자사업처) 4본부 체제. 정보화·디지털·개인정보보호는 사업관리본부 산하 '디지털홍보처'가 담당. 과거 'ICT추진단'(2021 단장 여하은)이 차세대 통합행정업무·중장기 정보화전략(ISP) 등 정보화사업을 수행했으나, 현 조직도에는 ICT추진단이 없고 디지털홍보처로 정보화 기능이 통합·개편된 것으로 판단. AI 기반 개인정보 유·노출 탐지시스템 도입(3년 연속 개인정보 관리 우수기관). 2019년 부→처 격상 등 조직개편 이력.</t>
         </is>
       </c>
     </row>
@@ -20545,17 +20545,17 @@
       </c>
       <c r="F268" s="3" t="inlineStr">
         <is>
-          <t>확인불가 (정보화·전산 전담조직 식별 안 됨 — 신설 소규모 박물관, 경영지원실 내 총무 기능에 포함 추정)</t>
+          <t>경영기획본부 (정보화·전산 전담 부서 없음 — 본부 내 관리기능에 포함, 전산은 공무직 직무로 운영)</t>
         </is>
       </c>
       <c r="G268" s="3" t="inlineStr">
         <is>
-          <t>확인불가</t>
+          <t>처·실(본부 산하) 수준의 전담 IT조직 미존재 — 정보화 기능이 경영기획본부 일반관리에 내포(전담조직 기준 확인불가)</t>
         </is>
       </c>
       <c r="H268" s="3" t="inlineStr">
         <is>
-          <t>확인불가 (전시 콘텐츠 측면의 '디지털' 기능은 학예/전시 부서 소관 추정)</t>
+          <t>경영기획본부 산하 부서: 기획예산·인사(인사부)·대외협력·재무회계·시설운영 (정보화/전산 전담팀 없음, '전산'은 공무직 직무)</t>
         </is>
       </c>
       <c r="I268" s="3" t="inlineStr">
@@ -20575,22 +20575,22 @@
       </c>
       <c r="L268" s="3" t="inlineStr">
         <is>
-          <t>확인불가</t>
+          <t>확인불가 (경영기획본부장(상임이사) 라인에서 정보화 총괄 추정)</t>
         </is>
       </c>
       <c r="M268" s="3" t="inlineStr">
         <is>
-          <t>확인불가</t>
+          <t>확인불가 (홈페이지 개인정보처리방침상 '경영지원실 운영지원팀장'이 개인정보보호책임자로 표기되나, 이는 국립해양박물관(부산) 방침을 그대로 차용한 표기로 보임 — 인천의 실제 부서·담당자와 불일치하여 신뢰 불가)</t>
         </is>
       </c>
       <c r="N268" s="3" t="inlineStr">
         <is>
-          <t>중(공식 홈페이지 메뉴구조 확인, 상세 조직도는 JS 렌더링으로 부서 세부 미확정)</t>
+          <t>중(공식 채용 직무기술서·입찰공고로 본부/부서 구성 및 전산 직무 확인 2출처, 단 상세 조직도는 JS 렌더링으로 미표출 / 개인정보처리방침은 타 기관 템플릿 차용으로 CISO 확정 불가)</t>
         </is>
       </c>
       <c r="O268" s="3" t="inlineStr">
         <is>
-          <t>2025년 개관한 신설 기관(해수부 산하 기타공공기관, 운영위탁: 산업연구원 채용시스템 활용 정황). 경영기획본부·학예연구본부 2본부 체계. '디지털박물관(디지털 실감영상실·VR 전시)' 등 디지털 전시 인프라 보유하나 IT 기획·운영 전담조직은 별도 확인 안 됨. AI는 교육프로그램('AI 북극 탐험대' 생성형 AI 활용 교육) 수준으로, AI 전담조직은 없음.</t>
+          <t>2024.12.11 개관한 신설 기관(해수부 산하 기타공공기관). 경영기획본부·학예연구본부 2본부 체계이며 본부 산하에 '부' 단위(예: 인사부) 구성. 채용 직무에 '전산'(공무직, 전산 기능사 이상)이 있어 IT 운영은 경영기획본부 내 전산 담당이 수행. 2026.4월 '아카이브 정보화설계 컨설팅 용역' 입찰 진행 — 정보화 사업은 추진 중이나 전담 정보화 조직은 신설 안 됨. '디지털박물관'(디지털 실감영상실·VR 전시)은 학예연구본부 산하 전시 기능. AI는 교육프로그램('AI 북극 탐험대' 등) 수준으로 AI 전담조직 없음.</t>
         </is>
       </c>
     </row>
@@ -20620,17 +20620,17 @@
       </c>
       <c r="F269" s="3" t="inlineStr">
         <is>
-          <t>정보화AI교육추진단</t>
+          <t>경영지원부 (산하 지식정보화팀이 정보화·정보보안·개인정보 총괄) / AI 교육사업은 별도 정보화AI교육추진단이 추진</t>
         </is>
       </c>
       <c r="G269" s="3" t="inlineStr">
         <is>
-          <t>단(추진단) (확인불가 — 본부/실 산하 여부 미확정)</t>
+          <t>팀 (본부 산하 경영지원부 내 '지식정보화팀')</t>
         </is>
       </c>
       <c r="H269" s="3" t="inlineStr">
         <is>
-          <t>확인불가 (정보화AI교육추진단이 정보화·AI 기능 통합 수행 추정)</t>
+          <t>지식정보화팀(정보화·정보보안·개인정보 실무, 경영지원부 산하), 정보화AI교육추진단(AI기반미래교육사업·ISP 추진)</t>
         </is>
       </c>
       <c r="I269" s="3" t="inlineStr">
@@ -20640,32 +20640,32 @@
       </c>
       <c r="J269" s="3" t="inlineStr">
         <is>
-          <t>정보화AI교육추진단</t>
+          <t>정보화AI교육추진단 (조직명에 'AI' 명시) / 주요사업 'AI기반미래교육사업' 전담</t>
         </is>
       </c>
       <c r="K269" s="3" t="inlineStr">
         <is>
-          <t>단(추진단) — 정보화 조직과 AI 기능이 동일 조직에 통합</t>
+          <t>단(추진단) — 정보화·AI 교육사업 추진 조직</t>
         </is>
       </c>
       <c r="L269" s="3" t="inlineStr">
         <is>
-          <t>확인불가</t>
+          <t>본부장 라인 총괄 추정 (개인정보보호책임자가 본부장 직책 — 동일 본부장이 정보화·보안 총괄 추정)</t>
         </is>
       </c>
       <c r="M269" s="3" t="inlineStr">
         <is>
-          <t>확인불가</t>
+          <t>개인정보보호책임자(CPO) 겸 보안 총괄: 본부장 김은희(02-3156-6002), 실무 담당부서 경영지원부 지식정보화팀(조형준·김하경) — CISO를 CPO/본부장이 겸하는 구조</t>
         </is>
       </c>
       <c r="N269" s="3" t="inlineStr">
         <is>
-          <t>중(공공데이터포털·기관 SNS·보도자료로 정보화AI교육추진단 확인, 공식 조직도 트리(상위 본부/실)는 JS 렌더링으로 미확정)</t>
+          <t>상(이러닝센터 공식 개인정보처리방침으로 CPO(본부장 김은희)·정보화 담당부서(경영지원부 지식정보화팀) 확정 + 공식 홈페이지/보도자료로 정보화AI교육추진단·AI사업 확인. 단 전체 조직도 트리(본부 정식 명칭)는 JS 렌더링으로 일부 미표출)</t>
         </is>
       </c>
       <c r="O269" s="3" t="inlineStr">
         <is>
-          <t>정보화 조직명에 'AI'를 명시한 '정보화AI교육추진단' 운영(공공데이터포털 관리부서명·기관 SNS로 확인, 대표번호 02-3156-6123). 2026.5월 'AI 기반 폭력 예방교육 혁신 정보화전략계획(ISP) 수립 사업' 착수 — 폭력예방교육 플랫폼의 AI·AX(AI Transformation) 대전환 추진. 'AI 및 AX전환 활용 역량강화 교육훈련' 등 자체 AI 역량강화도 진행.</t>
+          <t>약칭 '양평원'(KIGEPE). 정보화 조직명에 'AI'를 명시한 '정보화AI교육추진단' 운영. 2026.5월 'AI 기반 폭력 예방교육 혁신 정보화전략계획(ISP) 수립 사업' 착수(추진단 김수영 과장 02-3156-6124) — 폭력예방교육 플랫폼 AI·AX 대전환. 2026년 '모든 정보시스템 클라우드 전환' 보도 — 디지털 업무 혁신 추진. 본원(서울 은평) + 고양캠퍼스 2개소. 내부 정보화·정보보안·개인정보 거버넌스는 경영지원부 지식정보화팀이 수행.</t>
         </is>
       </c>
     </row>
@@ -20855,12 +20855,12 @@
       </c>
       <c r="H272" s="3" t="inlineStr">
         <is>
-          <t>정보화팀(정보화·전산 총괄), 의약품통합정보관리팀(의통팀, 의약품 통합정보시스템 운영) — 모두 기획경영본부 산하. 약물역학빅데이터팀(데이터 분석, 약물역학빅데이터 사업)도 운영</t>
+          <t>정보화팀(정보화·전산·정보보안 총괄, 기획경영본부 산하), 의약품통합정보관리팀(의약품 통합정보시스템 운영, 기획경영본부 산하), 약물역학빅데이터팀(데이터 분석, 의약품안전정보본부 산하)</t>
         </is>
       </c>
       <c r="I272" s="3" t="inlineStr">
         <is>
-          <t>확인불가 (별도 'AI' 명칭 전담조직은 현 조직도에서 미확인 — 약물역학빅데이터팀이 빅데이터·AI 기능 일부 수행 추정)</t>
+          <t>없음 (별도 'AI' 명칭 전담조직 미존재 — AI·LLM·CDM은 의약품안전정보본부 및 정보화팀이 본업(약물감시)에 적용)</t>
         </is>
       </c>
       <c r="J272" s="3" t="inlineStr">
@@ -20875,22 +20875,22 @@
       </c>
       <c r="L272" s="3" t="inlineStr">
         <is>
-          <t>확인불가 (기획경영본부장 라인에서 정보화 총괄 추정)</t>
+          <t>기획경영본부장 총괄 (정보화팀이 기획경영본부 산하)</t>
         </is>
       </c>
       <c r="M272" s="3" t="inlineStr">
         <is>
-          <t>확인불가</t>
+          <t>개인정보보호책임자(CPO) 겸 보안 총괄: 기획경영본부장 이성현(02-2172-6853), 보호 담당부서 정보화팀(팀장 김상윤, 02-2172-6731) — CISO를 본부장이 겸하는 구조</t>
         </is>
       </c>
       <c r="N272" s="3" t="inlineStr">
         <is>
-          <t>중(공식 홈페이지 조직도는 JS 렌더링으로 트리 미확정 / 기관 공식 채널·보도자료·공공기록으로 정보화팀·의통팀·약물역학빅데이터팀 등 확인)</t>
+          <t>상(KIDS 공식 개인정보처리방침으로 CPO(기획경영본부장 이성현)·정보화팀 확정 + 기관 공식 블로그·보도자료로 4본부 13팀 구조 및 AI 사업 추진 확인. 단 현행 조직도 트리는 일부 시점 차이 가능)</t>
         </is>
       </c>
       <c r="O272" s="3" t="inlineStr">
         <is>
-          <t>약칭 KIDS, 식약처 산하. 과거 공시 기준 4본부 13팀 5TF 체계. 'AI가 부작용을 예측' 등 AI·빅데이터 기반 약물감시·피해구제 전면 혁신 추진 중(2025~3년 단계, EMR 연계 공통데이터모델(CDM) 플랫폼 확대, AI 기반 비정형 EMR 표준화). 새 정부 AI 국정과제에 맞춰 자동화 기반 빅데이터·AI 약물감시 전환 추진. 다만 이는 본업(약물감시) 영역의 AI 적용으로, 전담 AI '조직' 신설 여부는 추가 확인 필요.</t>
+          <t>약칭 KIDS, 식약처 산하 국내 유일 약물감시 전담기관(2012 설립). 원장 중심 4본부 13팀 5TF — 기획경영본부(혁신경영팀·교육홍보팀·정보화팀·의약품통합정보관리팀), 의약품안전정보본부(안전정보관리팀·약물역학빅데이터팀·DUR정보팀), 의약품안전조사본부(의약품부작용피해구제팀·첨단바이오규제과학팀), 마약류통합정보관리본부(마약류시스템운영팀·마약류제도지원팀·마약류정보분석팀·마약류감사지원TF). 2025~2028 'AI·빅데이터 기반 능동형 약물감시 전면 개편'(LLM 기반 이상사례 검토 자동화, EMR-CDM 30→66개 기관 확대, 비정형 데이터 NLP 표준화, K-NASS 마약류 통합감시) 추진 — 다만 전담 AI '조직' 신설이 아니라 의약품안전정보본부·정보화팀이 본업에 AI 적용.</t>
         </is>
       </c>
     </row>
@@ -20995,17 +20995,17 @@
       </c>
       <c r="F274" s="3" t="inlineStr">
         <is>
-          <t>경영지원국 (별도 정보화 전담 부서 없음, 경영지원 기능 내 포함 추정)</t>
+          <t>기획홍보실 (산하 기획홍보팀이 정보화·정보시스템·개인정보 담당 — 별도 정보화 전담실 없음)</t>
         </is>
       </c>
       <c r="G274" s="3" t="inlineStr">
         <is>
-          <t>확인불가 (전담 IT조직 미확인 / 경영지원국 산하 기능 추정)</t>
+          <t>팀 (기획홍보실 산하 기획홍보팀)</t>
         </is>
       </c>
       <c r="H274" s="3" t="inlineStr">
         <is>
-          <t>확인불가 (경영지원국 산하: 법무1팀, 법무2팀, 법무3팀, 재무회계팀, 인사팀 — 정보화 전담팀 미확인)</t>
+          <t>기획홍보팀 (정보시스템 유지보수·정보화·개인정보보호 담당). 그 외 상위 조직: 변호사실·기획홍보실·경영지원국·감사실</t>
         </is>
       </c>
       <c r="I274" s="3" t="inlineStr">
@@ -21025,22 +21025,22 @@
       </c>
       <c r="L274" s="3" t="inlineStr">
         <is>
-          <t>확인불가 (경영지원국장 관할 추정)</t>
+          <t>기획홍보실장 총괄 추정 (정보화·정보시스템 담당이 기획홍보팀)</t>
         </is>
       </c>
       <c r="M274" s="3" t="inlineStr">
         <is>
-          <t>확인불가</t>
+          <t>개인정보보호책임자(CPO) 겸 보안 총괄: 기획홍보실 실장 박시준(02-2182-0074, gikang@kgls.or.kr), 보호담당자 기획홍보팀 팀장 정성윤·계장 강경일 — CISO를 기획홍보실장이 겸하는 구조</t>
         </is>
       </c>
       <c r="N274" s="3" t="inlineStr">
         <is>
-          <t>중(공식 1출처+위키, IT부서 미확인)</t>
+          <t>상(공식 개인정보처리방침(2025.06.01 시행)으로 IT·개인정보 담당부서(기획홍보실/기획홍보팀)·CPO(기획홍보실장 박시준) 확정 + 공식 조직도/구성원소개로 실·국 구조 확인. 단 조직도 본문은 이미지로만 제공되어 기획홍보실 내 팀 세부 분할은 부분 확인)</t>
         </is>
       </c>
       <c r="O274" s="3" t="inlineStr">
         <is>
-          <t>국가소송 수행 전문 국가 로펌(변호사 중심 조직). 조직은 변호사실(다수 변호사팀)·기획홍보실·경영지원국·감사실로 구성. 정보화/전산 전담 부서명이 공식 조직도(이미지)·위키 모두에서 별도 확인되지 않음 → 경영지원국 일반관리 기능에 포함된 것으로 추정.</t>
+          <t>국가소송 수행 전문 국가 로펌(변호사 중심 조직, 2008.2 출범). 조직은 변호사실(분야별 변호사팀)·기획홍보실·경영지원국·감사실로 구성. 정보화·전산·정보시스템 운영과 개인정보보호는 '기획홍보실/기획홍보팀'이 담당(개인정보처리방침으로 확인) — 당초 추정한 경영지원국이 아님. 시스템 유지보수는 로타임비즈텍 위탁. 2024년 공공기관 개인정보 보호수준 평가 'A'등급. AI 전담조직·연구조직은 없음(법률서비스 수행 기관).</t>
         </is>
       </c>
     </row>
@@ -21070,52 +21070,52 @@
       </c>
       <c r="F275" s="3" t="inlineStr">
         <is>
-          <t>지식정보팀 (경영지원실 산하)</t>
+          <t>경영지원실 (산하 지식정보팀이 내부 정보화·정보보안 담당) / 데이터·AI는 사법무디지털센터(정보통계팀·AI·법·정책연구팀)가 수행</t>
         </is>
       </c>
       <c r="G275" s="3" t="inlineStr">
         <is>
-          <t>팀</t>
+          <t>팀 (경영지원실 산하 지식정보팀 / 사법무디지털센터 산하 정보통계팀)</t>
         </is>
       </c>
       <c r="H275" s="3" t="inlineStr">
         <is>
-          <t>지식정보팀 (경영지원실 산하 추정)</t>
+          <t>지식정보팀(내부 정보화·정보보안·개인정보, 경영지원실 산하), 정보통계팀(기술·개발·내부 통계서비스·AI lab 운영, 사법무디지털센터 산하)</t>
         </is>
       </c>
       <c r="I275" s="3" t="inlineStr">
         <is>
-          <t>확인불가 (전담 AI조직 미확인)</t>
+          <t>있음</t>
         </is>
       </c>
       <c r="J275" s="3" t="inlineStr">
         <is>
-          <t>확인불가</t>
+          <t>AI·법·정책연구팀 (사법무디지털센터 산하) — 정보통계팀(AI lab)과 병행</t>
         </is>
       </c>
       <c r="K275" s="3" t="inlineStr">
         <is>
-          <t>확인불가</t>
+          <t>팀 (사법무디지털센터 산하)</t>
         </is>
       </c>
       <c r="L275" s="3" t="inlineStr">
         <is>
-          <t>확인불가 (경영지원실장 관할 추정)</t>
+          <t>경영지원실장 총괄 추정 (내부 정보화 담당이 경영지원실 지식정보팀)</t>
         </is>
       </c>
       <c r="M275" s="3" t="inlineStr">
         <is>
-          <t>확인불가</t>
+          <t>개인정보보호책임자(CPO) 겸 보안 총괄: 경영지원실장 김병규(02-3460-5158, kbg@kicj.re.kr), 보호담당자 경영지원실 지식정보팀장 전태윤(02-3460-5112) — CISO를 경영지원실장이 겸하는 구조</t>
         </is>
       </c>
       <c r="N275" s="3" t="inlineStr">
         <is>
-          <t>중(위키 1출처, 공식 조직도 직접 미확인)</t>
+          <t>상(개인정보처리방침으로 CPO(경영지원실장 김병규)·담당부서(지식정보팀) 확정 + 인터뷰·R&amp;D 자료로 사법무디지털센터·AI·법·정책연구팀 확인. 단 공식 홈페이지(kicj.re.kr)가 WebFetch 403·tavily 일시오류로 직접 트리는 미열람, 검색 스니펫·교차출처로 확정)</t>
         </is>
       </c>
       <c r="O275" s="3" t="inlineStr">
         <is>
-          <t>형사정책·법무 전문 연구기관. 연구실(형사법·일반범죄·특수범죄·사법개혁·인권미래정책·범죄통계 등)+기획조정실+국제전략협의실+경영지원실+감사실 구성. 정보화 기능은 경영지원실 산하 지식정보팀이 담당하는 것으로 확인. 범죄통계 통합DB 등 데이터 자산 보유(공공데이터 개방).</t>
+          <t>형사정책·법무 전문 연구기관(경제·인문사회연구회 소관, 영문약칭 KICJ). 2023년 '사법무디지털센터' 신설 — 산하에 정보통계팀(기술·개발, AI lab 운영)과 AI·법·정책연구팀(생성형 AI 활용 형사·법무 정책연구·빅데이터 분석·융합연구)을 두어 AI 전담 연구 기능 보유. 2024년 'AI 전자감독·재범위험도분석·일탈탐지' 국가 R&amp;D 수행. 형사사법통계(CCJS)·범죄통계 통합DB 등 데이터 자산 보유. 내부 정보화·정보보안은 경영지원실(총무인사팀·지식정보팀·재무회계팀) 산하 지식정보팀이 담당.</t>
         </is>
       </c>
     </row>
@@ -21280,11 +21280,11 @@
         </is>
       </c>
       <c r="E5" s="5" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>35.9%</t>
+          <t>36.4%</t>
         </is>
       </c>
       <c r="G5" s="5" t="n">
@@ -21314,11 +21314,11 @@
         </is>
       </c>
       <c r="E6" s="5" t="n">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>49.6%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="G6" s="5" t="n">
@@ -21383,11 +21383,11 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>51.5%</t>
+          <t>53.6%</t>
         </is>
       </c>
     </row>
@@ -21398,11 +21398,11 @@
         </is>
       </c>
       <c r="B12" s="5" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>25.9%</t>
+          <t>26.6%</t>
         </is>
       </c>
     </row>
@@ -21413,11 +21413,11 @@
         </is>
       </c>
       <c r="B13" s="5" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>8.8%</t>
+          <t>5.8%</t>
         </is>
       </c>
     </row>
@@ -21459,11 +21459,11 @@
         </is>
       </c>
       <c r="B17" s="5" t="n">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>49.6%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -21474,11 +21474,11 @@
         </is>
       </c>
       <c r="B18" s="5" t="n">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>41.6%</t>
+          <t>42.3%</t>
         </is>
       </c>
     </row>
@@ -21489,11 +21489,11 @@
         </is>
       </c>
       <c r="B19" s="5" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>8.8%</t>
+          <t>7.7%</t>
         </is>
       </c>
     </row>
@@ -21535,11 +21535,11 @@
         </is>
       </c>
       <c r="B23" s="5" t="n">
-        <v>206</v>
+        <v>218</v>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>75.2%</t>
+          <t>79.6%</t>
         </is>
       </c>
     </row>
@@ -21550,11 +21550,11 @@
         </is>
       </c>
       <c r="B24" s="5" t="n">
-        <v>68</v>
+        <v>56</v>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>24.8%</t>
+          <t>20.4%</t>
         </is>
       </c>
     </row>
@@ -21599,7 +21599,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H31"/>
+  <dimension ref="A1:H25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -22482,7 +22482,7 @@
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>중(공식 홈페이지 조직도 이미지 + 2026 개편 보도 다수 교차확인, 단 정확한 소속 라인 이미지 미파싱)</t>
+          <t>상(공식 홈페이지 개인정보처리방침으로 경영지원실·디지털전환팀 소속·CPO 확인 + 2026 개편 보도 다수 교차확인)</t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr">
@@ -22492,7 +22492,7 @@
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>디지털전환팀(DAX팀) — 행정·경영지원 라인 소속 (추정)</t>
+          <t>경영지원실 (산하 디지털전환팀(DAX팀)이 지식정보·전산·디지털전환 담당)</t>
         </is>
       </c>
       <c r="H23" s="3" t="inlineStr">
@@ -22544,7 +22544,7 @@
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>국립대구과학관</t>
+          <t>한국저작권보호원</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
@@ -22558,266 +22558,26 @@
         </is>
       </c>
       <c r="D25" s="3" t="n">
-        <v>147</v>
+        <v>104.8</v>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>중(실 단위 조직명은 보도·인사자료로 확인, 전산 전담부서명·소속은 미확정)</t>
+          <t>상(공식 홈페이지 조직도 + 공공데이터포털 관리부서 표기 교차확인)</t>
         </is>
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t>IT최상위 확인불가 / AI전담 확인불가</t>
+          <t>AI전담 확인불가</t>
         </is>
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>확인불가 (별도 IT 본부·처·실 없음 — 실 단위 조직 중 '경영관리실'이 전산·정보화 행정을 겸장하는 것으로 추정)</t>
+          <t>정보기술부</t>
         </is>
       </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
-          <t>확인불가 (전담조직 미확인)</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="3" t="inlineStr">
-        <is>
-          <t>한국로봇산업진흥원</t>
-        </is>
-      </c>
-      <c r="B26" s="3" t="inlineStr">
-        <is>
-          <t>기타</t>
-        </is>
-      </c>
-      <c r="C26" s="3" t="inlineStr">
-        <is>
-          <t>기타공공기관</t>
-        </is>
-      </c>
-      <c r="D26" s="3" t="n">
-        <v>117</v>
-      </c>
-      <c r="E26" s="3" t="inlineStr">
-        <is>
-          <t>중(공식 홈페이지 도메인 확정 + 2026.5 개편 보도 교차, 내부 정보화 조직 직제는 미확인)</t>
-        </is>
-      </c>
-      <c r="F26" s="3" t="inlineStr">
-        <is>
-          <t>IT최상위 확인불가</t>
-        </is>
-      </c>
-      <c r="G26" s="3" t="inlineStr">
-        <is>
-          <t>확인불가 (별도 정보화 본부·실 없음 — 2본부 2실 체제, 정보화는 경영기획실 산하 기능으로 추정)</t>
-        </is>
-      </c>
-      <c r="H26" s="3" t="inlineStr">
-        <is>
-          <t>있음(AX 본부 형태 — 단, AI 기술전담이 아닌 로봇산업진흥 본부)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="3" t="inlineStr">
-        <is>
-          <t>한국여성정책연구원</t>
-        </is>
-      </c>
-      <c r="B27" s="3" t="inlineStr">
-        <is>
-          <t>기타</t>
-        </is>
-      </c>
-      <c r="C27" s="3" t="inlineStr">
-        <is>
-          <t>기타공공기관</t>
-        </is>
-      </c>
-      <c r="D27" s="3" t="n">
-        <v>116</v>
-      </c>
-      <c r="E27" s="3" t="inlineStr">
-        <is>
-          <t>중(공식 1출처 + 위키 보조 / IT·AI 세부조직 확인불가)</t>
-        </is>
-      </c>
-      <c r="F27" s="3" t="inlineStr">
-        <is>
-          <t>IT최상위 확인불가</t>
-        </is>
-      </c>
-      <c r="G27" s="3" t="inlineStr">
-        <is>
-          <t>확인불가 (경영지원본부 산하 추정)</t>
-        </is>
-      </c>
-      <c r="H27" s="3" t="inlineStr">
-        <is>
-          <t>없음 (확인불가에 가까움 — 별도 AI조직 단서 없음)</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="3" t="inlineStr">
-        <is>
-          <t>국립인천해양박물관</t>
-        </is>
-      </c>
-      <c r="B28" s="3" t="inlineStr">
-        <is>
-          <t>기타</t>
-        </is>
-      </c>
-      <c r="C28" s="3" t="inlineStr">
-        <is>
-          <t>기타공공기관</t>
-        </is>
-      </c>
-      <c r="D28" s="3" t="n">
-        <v>105</v>
-      </c>
-      <c r="E28" s="3" t="inlineStr">
-        <is>
-          <t>중(공식 홈페이지 메뉴구조 확인, 상세 조직도는 JS 렌더링으로 부서 세부 미확정)</t>
-        </is>
-      </c>
-      <c r="F28" s="3" t="inlineStr">
-        <is>
-          <t>IT최상위 확인불가</t>
-        </is>
-      </c>
-      <c r="G28" s="3" t="inlineStr">
-        <is>
-          <t>확인불가 (정보화·전산 전담조직 식별 안 됨 — 신설 소규모 박물관, 경영지원실 내 총무 기능에 포함 추정)</t>
-        </is>
-      </c>
-      <c r="H28" s="3" t="inlineStr">
-        <is>
-          <t>없음</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="3" t="inlineStr">
-        <is>
-          <t>한국저작권보호원</t>
-        </is>
-      </c>
-      <c r="B29" s="3" t="inlineStr">
-        <is>
-          <t>기타</t>
-        </is>
-      </c>
-      <c r="C29" s="3" t="inlineStr">
-        <is>
-          <t>기타공공기관</t>
-        </is>
-      </c>
-      <c r="D29" s="3" t="n">
-        <v>104.8</v>
-      </c>
-      <c r="E29" s="3" t="inlineStr">
-        <is>
-          <t>상(공식 홈페이지 조직도 + 공공데이터포털 관리부서 표기 교차확인)</t>
-        </is>
-      </c>
-      <c r="F29" s="3" t="inlineStr">
-        <is>
-          <t>AI전담 확인불가</t>
-        </is>
-      </c>
-      <c r="G29" s="3" t="inlineStr">
-        <is>
-          <t>정보기술부</t>
-        </is>
-      </c>
-      <c r="H29" s="3" t="inlineStr">
-        <is>
           <t>확인불가 (별도 AI 전담조직 식별 안 됨)</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="3" t="inlineStr">
-        <is>
-          <t>한국의약품안전관리원</t>
-        </is>
-      </c>
-      <c r="B30" s="3" t="inlineStr">
-        <is>
-          <t>기타</t>
-        </is>
-      </c>
-      <c r="C30" s="3" t="inlineStr">
-        <is>
-          <t>기타공공기관</t>
-        </is>
-      </c>
-      <c r="D30" s="3" t="n">
-        <v>103.4</v>
-      </c>
-      <c r="E30" s="3" t="inlineStr">
-        <is>
-          <t>중(공식 홈페이지 조직도는 JS 렌더링으로 트리 미확정 / 기관 공식 채널·보도자료·공공기록으로 정보화팀·의통팀·약물역학빅데이터팀 등 확인)</t>
-        </is>
-      </c>
-      <c r="F30" s="3" t="inlineStr">
-        <is>
-          <t>AI전담 확인불가</t>
-        </is>
-      </c>
-      <c r="G30" s="3" t="inlineStr">
-        <is>
-          <t>정보화팀 (기획경영본부 산하)</t>
-        </is>
-      </c>
-      <c r="H30" s="3" t="inlineStr">
-        <is>
-          <t>확인불가 (별도 'AI' 명칭 전담조직은 현 조직도에서 미확인 — 약물역학빅데이터팀이 빅데이터·AI 기능 일부 수행 추정)</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="3" t="inlineStr">
-        <is>
-          <t>한국형사·법무정책연구원</t>
-        </is>
-      </c>
-      <c r="B31" s="3" t="inlineStr">
-        <is>
-          <t>기타</t>
-        </is>
-      </c>
-      <c r="C31" s="3" t="inlineStr">
-        <is>
-          <t>기타공공기관</t>
-        </is>
-      </c>
-      <c r="D31" s="3" t="n">
-        <v>101</v>
-      </c>
-      <c r="E31" s="3" t="inlineStr">
-        <is>
-          <t>중(위키 1출처, 공식 조직도 직접 미확인)</t>
-        </is>
-      </c>
-      <c r="F31" s="3" t="inlineStr">
-        <is>
-          <t>AI전담 확인불가</t>
-        </is>
-      </c>
-      <c r="G31" s="3" t="inlineStr">
-        <is>
-          <t>지식정보팀 (경영지원실 산하)</t>
-        </is>
-      </c>
-      <c r="H31" s="3" t="inlineStr">
-        <is>
-          <t>확인불가 (전담 AI조직 미확인)</t>
         </is>
       </c>
     </row>
